--- a/DataGen/LTM/synthetic_demand_groups.xlsx
+++ b/DataGen/LTM/synthetic_demand_groups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,19 +470,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>615</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>561</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -493,16 +493,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>230</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>157</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>515</v>
+        <v>488</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -516,19 +516,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>787</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>849</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>627</v>
+        <v>507</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -539,16 +539,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>630</v>
+        <v>515</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -562,16 +562,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>340</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>370</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>663</v>
+        <v>623</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -585,16 +585,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>661</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>671</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>680</v>
+        <v>627</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -608,19 +608,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>813</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>860</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -631,19 +631,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>699</v>
+        <v>663</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -654,19 +654,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>479</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>430</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>704</v>
+        <v>680</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -677,19 +677,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>846</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>751</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -700,16 +700,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>190</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>165</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>726</v>
+        <v>699</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -723,13 +723,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>265</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>738</v>
+        <v>704</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -746,19 +746,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>376</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>630</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>773</v>
+        <v>704</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -769,16 +769,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>461</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>420</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>810</v>
+        <v>726</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -792,13 +792,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>817</v>
+        <v>738</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -815,19 +815,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>461</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>450</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>825</v>
+        <v>773</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -838,19 +838,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>827</v>
+        <v>810</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -861,16 +861,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>813</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>851</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>890</v>
+        <v>817</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -884,16 +884,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>751</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>898</v>
+        <v>825</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -907,19 +907,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>575</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>580</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>921</v>
+        <v>827</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -930,16 +930,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>810</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>813</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>943</v>
+        <v>890</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -953,16 +953,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>968</v>
+        <v>898</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -976,19 +976,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>461</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>530</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>969</v>
+        <v>921</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -999,16 +999,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>621</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>657</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>972</v>
+        <v>943</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1022,13 +1022,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>230</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1045,16 +1045,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>849</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>657</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>982</v>
+        <v>969</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1068,16 +1068,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>187</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>982</v>
+        <v>972</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1091,19 +1091,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>849</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>461</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -1114,19 +1114,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1000</v>
+        <v>982</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -1137,19 +1137,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>161</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>1030</v>
+        <v>982</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -1160,13 +1160,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>265</v>
+        <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1033</v>
+        <v>990</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -1183,16 +1183,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>336</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>370</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>1035</v>
+        <v>1000</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -1206,19 +1206,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>479</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>707</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>1043</v>
+        <v>1030</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -1229,16 +1229,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>183</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>1054</v>
+        <v>1033</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -1252,16 +1252,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>671</v>
+        <v>8</v>
       </c>
       <c r="C36" t="n">
-        <v>661</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>1057</v>
+        <v>1035</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -1275,19 +1275,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>163</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1089</v>
+        <v>1043</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -1298,19 +1298,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>230</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>1092</v>
+        <v>1054</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -1321,13 +1321,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>161</v>
+        <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>1112</v>
+        <v>1057</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -1344,13 +1344,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>169</v>
+        <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>1117</v>
+        <v>1089</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -1367,16 +1367,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>151</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>1122</v>
+        <v>1092</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1390,16 +1390,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>190</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -1413,16 +1413,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>1127</v>
+        <v>1117</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -1436,16 +1436,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>710</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>751</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>1143</v>
+        <v>1122</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1459,16 +1459,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>1151</v>
+        <v>1125</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -1482,19 +1482,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>159</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>1171</v>
+        <v>1127</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -1505,13 +1505,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>270</v>
+        <v>7</v>
       </c>
       <c r="C47" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1178</v>
+        <v>1143</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -1528,19 +1528,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>329</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>259</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>1178</v>
+        <v>1151</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -1551,13 +1551,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>185</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>1205</v>
+        <v>1171</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
@@ -1574,19 +1574,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>561</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>573</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>1209</v>
+        <v>1178</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -1597,16 +1597,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>157</v>
+        <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>173</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>1213</v>
+        <v>1178</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>773</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>787</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>1215</v>
+        <v>1205</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1643,19 +1643,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>163</v>
+        <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>1218</v>
+        <v>1209</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -1666,16 +1666,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>190</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>1228</v>
+        <v>1213</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1689,16 +1689,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>760</v>
+        <v>7</v>
       </c>
       <c r="C55" t="n">
-        <v>661</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1243</v>
+        <v>1215</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1712,19 +1712,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>185</v>
+        <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>1258</v>
+        <v>1218</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1735,19 +1735,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>1259</v>
+        <v>1228</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -1758,16 +1758,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="C58" t="n">
-        <v>330</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1274</v>
+        <v>1243</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -1781,19 +1781,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>740</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>615</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>1284</v>
+        <v>1258</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -1804,16 +1804,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>265</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>1286</v>
+        <v>1259</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -1827,13 +1827,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>461</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>479</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>1292</v>
+        <v>1274</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -1850,22 +1850,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="C62" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>484</v>
+        <v>1284</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1873,22 +1873,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>779</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>773</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>491</v>
+        <v>1286</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -1896,13 +1896,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>370</v>
+        <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>497</v>
+        <v>1292</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1919,13 +1919,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>756</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>751</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -1942,19 +1942,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>820</v>
+        <v>7</v>
       </c>
       <c r="C66" t="n">
-        <v>791</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>522</v>
+        <v>491</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -1965,13 +1965,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>766</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>530</v>
+        <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -1988,16 +1988,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="C68" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -2011,19 +2011,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>230</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>555</v>
+        <v>530</v>
       </c>
       <c r="E69" t="n">
         <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>2</v>
@@ -2034,19 +2034,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="D70" t="n">
-        <v>565</v>
+        <v>532</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
         <v>2</v>
@@ -2057,16 +2057,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>849</v>
+        <v>7</v>
       </c>
       <c r="C71" t="n">
-        <v>820</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -2080,19 +2080,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>561</v>
+        <v>8</v>
       </c>
       <c r="C72" t="n">
-        <v>563</v>
+        <v>7</v>
       </c>
       <c r="D72" t="n">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>2</v>
@@ -2103,19 +2103,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>530</v>
+        <v>8</v>
       </c>
       <c r="C73" t="n">
-        <v>575</v>
+        <v>7</v>
       </c>
       <c r="D73" t="n">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
         <v>2</v>
@@ -2126,13 +2126,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>746</v>
+        <v>5</v>
       </c>
       <c r="C74" t="n">
-        <v>710</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2149,19 +2149,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>622</v>
+        <v>583</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>2</v>
@@ -2172,13 +2172,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>410</v>
+        <v>7</v>
       </c>
       <c r="C76" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>640</v>
+        <v>597</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -2195,19 +2195,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>430</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>540</v>
+        <v>8</v>
       </c>
       <c r="D77" t="n">
-        <v>659</v>
+        <v>622</v>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
         <v>2</v>
@@ -2218,16 +2218,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>849</v>
+        <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -2241,16 +2241,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>479</v>
+        <v>7</v>
       </c>
       <c r="C79" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2264,16 +2264,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>730</v>
+        <v>9</v>
       </c>
       <c r="C80" t="n">
-        <v>657</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2287,13 +2287,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>173</v>
+        <v>6</v>
       </c>
       <c r="C81" t="n">
-        <v>185</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>699</v>
+        <v>671</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2310,19 +2310,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>561</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>510</v>
+        <v>9</v>
       </c>
       <c r="D82" t="n">
-        <v>716</v>
+        <v>675</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
         <v>2</v>
@@ -2333,19 +2333,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>217</v>
+        <v>6</v>
       </c>
       <c r="C83" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>2</v>
@@ -2356,13 +2356,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="D84" t="n">
-        <v>804</v>
+        <v>716</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -2379,19 +2379,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>390</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>320</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>829</v>
+        <v>725</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>2</v>
@@ -2402,16 +2402,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>751</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
-        <v>836</v>
+        <v>732</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2425,19 +2425,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>561</v>
+        <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>575</v>
+        <v>10</v>
       </c>
       <c r="D87" t="n">
-        <v>923</v>
+        <v>756</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>2</v>
@@ -2448,19 +2448,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>250</v>
+        <v>7</v>
       </c>
       <c r="C88" t="n">
-        <v>219</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>932</v>
+        <v>804</v>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>2</v>
@@ -2471,19 +2471,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>760</v>
+        <v>7</v>
       </c>
       <c r="C89" t="n">
-        <v>615</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>953</v>
+        <v>829</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>2</v>
@@ -2494,19 +2494,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>954</v>
+        <v>836</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
         <v>2</v>
@@ -2517,19 +2517,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>766</v>
+        <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>615</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>969</v>
+        <v>897</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>2</v>
@@ -2540,19 +2540,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>175</v>
+        <v>9</v>
       </c>
       <c r="C92" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>976</v>
+        <v>923</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
@@ -2563,16 +2563,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>147</v>
+        <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>976</v>
+        <v>932</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -2586,13 +2586,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>173</v>
+        <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1045</v>
+        <v>953</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -2609,16 +2609,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>1049</v>
+        <v>954</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -2632,16 +2632,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="C96" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1060</v>
+        <v>969</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
@@ -2655,19 +2655,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>615</v>
+        <v>2</v>
       </c>
       <c r="C97" t="n">
-        <v>730</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1083</v>
+        <v>972</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>2</v>
@@ -2678,19 +2678,19 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>530</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>550</v>
+        <v>7</v>
       </c>
       <c r="D98" t="n">
-        <v>1091</v>
+        <v>976</v>
       </c>
       <c r="E98" t="n">
         <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
         <v>2</v>
@@ -2701,19 +2701,19 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>550</v>
+        <v>9</v>
       </c>
       <c r="C99" t="n">
-        <v>540</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1115</v>
+        <v>1049</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>2</v>
@@ -2724,16 +2724,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>630</v>
+        <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>621</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1120</v>
+        <v>1049</v>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
@@ -2747,16 +2747,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>540</v>
+        <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>461</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1133</v>
+        <v>1060</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -2770,13 +2770,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>169</v>
+        <v>2</v>
       </c>
       <c r="C102" t="n">
-        <v>167</v>
+        <v>8</v>
       </c>
       <c r="D102" t="n">
-        <v>1136</v>
+        <v>1083</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -2793,16 +2793,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>326</v>
+        <v>7</v>
       </c>
       <c r="C103" t="n">
-        <v>350</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>1138</v>
+        <v>1084</v>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -2816,19 +2816,19 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>760</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>787</v>
+        <v>7</v>
       </c>
       <c r="D104" t="n">
-        <v>1142</v>
+        <v>1091</v>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
         <v>2</v>
@@ -2839,19 +2839,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>219</v>
+        <v>7</v>
       </c>
       <c r="C105" t="n">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1161</v>
+        <v>1115</v>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
         <v>2</v>
@@ -2862,16 +2862,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>169</v>
+        <v>7</v>
       </c>
       <c r="D106" t="n">
-        <v>1161</v>
+        <v>1120</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -2885,16 +2885,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>151</v>
+        <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>1165</v>
+        <v>1133</v>
       </c>
       <c r="E107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
@@ -2908,19 +2908,19 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>540</v>
+        <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>580</v>
+        <v>8</v>
       </c>
       <c r="D108" t="n">
-        <v>1169</v>
+        <v>1136</v>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
         <v>2</v>
@@ -2931,19 +2931,19 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>161</v>
+        <v>7</v>
       </c>
       <c r="C109" t="n">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>1170</v>
+        <v>1138</v>
       </c>
       <c r="E109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
         <v>2</v>
@@ -2954,16 +2954,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>173</v>
+        <v>7</v>
       </c>
       <c r="C110" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>1220</v>
+        <v>1142</v>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
@@ -2977,16 +2977,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>751</v>
+        <v>1</v>
       </c>
       <c r="C111" t="n">
-        <v>756</v>
+        <v>9</v>
       </c>
       <c r="D111" t="n">
-        <v>1224</v>
+        <v>1161</v>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -3000,16 +3000,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>540</v>
+        <v>1</v>
       </c>
       <c r="C112" t="n">
-        <v>621</v>
+        <v>7</v>
       </c>
       <c r="D112" t="n">
-        <v>1230</v>
+        <v>1161</v>
       </c>
       <c r="E112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -3023,16 +3023,16 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>330</v>
+        <v>7</v>
       </c>
       <c r="C113" t="n">
-        <v>306</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>1237</v>
+        <v>1169</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -3046,19 +3046,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>661</v>
+        <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>851</v>
+        <v>7</v>
       </c>
       <c r="D114" t="n">
-        <v>1255</v>
+        <v>1170</v>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
         <v>2</v>
@@ -3069,16 +3069,16 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="D115" t="n">
-        <v>1270</v>
+        <v>1206</v>
       </c>
       <c r="E115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -3092,13 +3092,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>621</v>
+        <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>510</v>
+        <v>4</v>
       </c>
       <c r="D116" t="n">
-        <v>1271</v>
+        <v>1220</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3115,19 +3115,19 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>183</v>
+        <v>7</v>
       </c>
       <c r="D117" t="n">
-        <v>1279</v>
+        <v>1230</v>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
         <v>2</v>
@@ -3138,13 +3138,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>621</v>
+        <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>561</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>1297</v>
+        <v>1237</v>
       </c>
       <c r="E118" t="n">
         <v>1</v>
@@ -3161,16 +3161,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>580</v>
+        <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>540</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>1299</v>
+        <v>1255</v>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -3184,19 +3184,19 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>760</v>
+        <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>779</v>
+        <v>7</v>
       </c>
       <c r="D120" t="n">
-        <v>1307</v>
+        <v>1270</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>2</v>
@@ -3207,19 +3207,19 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>810</v>
+        <v>7</v>
       </c>
       <c r="C121" t="n">
-        <v>849</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>1314</v>
+        <v>1271</v>
       </c>
       <c r="E121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
         <v>2</v>
@@ -3230,22 +3230,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>846</v>
+        <v>7</v>
       </c>
       <c r="C122" t="n">
-        <v>840</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>480</v>
+        <v>1271</v>
       </c>
       <c r="E122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -3253,22 +3253,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>480</v>
+        <v>1279</v>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -3276,22 +3276,22 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>219</v>
+        <v>7</v>
       </c>
       <c r="C124" t="n">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>484</v>
+        <v>1297</v>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -3299,13 +3299,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>575</v>
+        <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>510</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>491</v>
+        <v>1299</v>
       </c>
       <c r="E125" t="n">
         <v>2</v>
@@ -3314,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -3322,22 +3322,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>167</v>
+        <v>4</v>
       </c>
       <c r="C126" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>502</v>
+        <v>1307</v>
       </c>
       <c r="E126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -3345,22 +3345,22 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>219</v>
+        <v>7</v>
       </c>
       <c r="C127" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>518</v>
+        <v>1314</v>
       </c>
       <c r="E127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3368,19 +3368,19 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>329</v>
+        <v>7</v>
       </c>
       <c r="C128" t="n">
-        <v>326</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
         <v>3</v>
@@ -3391,19 +3391,19 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>376</v>
+        <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>390</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
-        <v>533</v>
+        <v>484</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
         <v>3</v>
@@ -3414,16 +3414,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>175</v>
+        <v>7</v>
       </c>
       <c r="D130" t="n">
-        <v>537</v>
+        <v>491</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -3437,19 +3437,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>175</v>
+        <v>9</v>
       </c>
       <c r="C131" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>549</v>
+        <v>502</v>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
         <v>3</v>
@@ -3460,13 +3460,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>665</v>
+        <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>661</v>
+        <v>4</v>
       </c>
       <c r="D132" t="n">
-        <v>564</v>
+        <v>520</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -3483,16 +3483,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>580</v>
+        <v>8</v>
       </c>
       <c r="C133" t="n">
-        <v>540</v>
+        <v>7</v>
       </c>
       <c r="D133" t="n">
-        <v>570</v>
+        <v>533</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -3506,13 +3506,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>860</v>
+        <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>813</v>
+        <v>7</v>
       </c>
       <c r="D134" t="n">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -3529,19 +3529,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>430</v>
+        <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="D135" t="n">
-        <v>596</v>
+        <v>560</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
         <v>3</v>
@@ -3552,16 +3552,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>550</v>
+        <v>7</v>
       </c>
       <c r="C136" t="n">
-        <v>760</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>644</v>
+        <v>564</v>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" t="n">
         <v>1</v>
@@ -3575,19 +3575,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>482</v>
+        <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>479</v>
+        <v>7</v>
       </c>
       <c r="D137" t="n">
-        <v>649</v>
+        <v>574</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
         <v>3</v>
@@ -3598,19 +3598,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>390</v>
+        <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>217</v>
+        <v>7</v>
       </c>
       <c r="D138" t="n">
-        <v>669</v>
+        <v>596</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
         <v>3</v>
@@ -3621,19 +3621,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>157</v>
+        <v>9</v>
       </c>
       <c r="C139" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>692</v>
+        <v>617</v>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>3</v>
@@ -3644,16 +3644,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>217</v>
+        <v>9</v>
       </c>
       <c r="C140" t="n">
-        <v>223</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>696</v>
+        <v>645</v>
       </c>
       <c r="E140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -3667,13 +3667,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>573</v>
+        <v>7</v>
       </c>
       <c r="C141" t="n">
-        <v>657</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>718</v>
+        <v>686</v>
       </c>
       <c r="E141" t="n">
         <v>1</v>
@@ -3690,19 +3690,19 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>219</v>
+        <v>7</v>
       </c>
       <c r="D142" t="n">
-        <v>729</v>
+        <v>692</v>
       </c>
       <c r="E142" t="n">
         <v>1</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
         <v>3</v>
@@ -3713,19 +3713,19 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>173</v>
+        <v>7</v>
       </c>
       <c r="C143" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>738</v>
+        <v>718</v>
       </c>
       <c r="E143" t="n">
         <v>2</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>3</v>
@@ -3736,19 +3736,19 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>320</v>
+        <v>7</v>
       </c>
       <c r="C144" t="n">
-        <v>326</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>761</v>
+        <v>729</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
         <v>3</v>
@@ -3759,16 +3759,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>751</v>
+        <v>7</v>
       </c>
       <c r="C145" t="n">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>784</v>
+        <v>738</v>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -3782,19 +3782,19 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>370</v>
+        <v>7</v>
       </c>
       <c r="C146" t="n">
-        <v>326</v>
+        <v>8</v>
       </c>
       <c r="D146" t="n">
-        <v>795</v>
+        <v>761</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
         <v>3</v>
@@ -3805,16 +3805,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>630</v>
+        <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>573</v>
+        <v>2</v>
       </c>
       <c r="D147" t="n">
-        <v>837</v>
+        <v>784</v>
       </c>
       <c r="E147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
         <v>1</v>
@@ -3828,19 +3828,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>260</v>
+        <v>8</v>
       </c>
       <c r="C148" t="n">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="D148" t="n">
-        <v>848</v>
+        <v>795</v>
       </c>
       <c r="E148" t="n">
         <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
         <v>3</v>
@@ -3851,16 +3851,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>173</v>
+        <v>7</v>
       </c>
       <c r="C149" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>852</v>
+        <v>827</v>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
@@ -3874,19 +3874,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>825</v>
+        <v>7</v>
       </c>
       <c r="C150" t="n">
-        <v>707</v>
+        <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>853</v>
+        <v>837</v>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G150" t="n">
         <v>3</v>
@@ -3897,13 +3897,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="C151" t="n">
-        <v>269</v>
+        <v>3</v>
       </c>
       <c r="D151" t="n">
-        <v>864</v>
+        <v>839</v>
       </c>
       <c r="E151" t="n">
         <v>1</v>
@@ -3920,19 +3920,19 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>440</v>
+        <v>9</v>
       </c>
       <c r="C152" t="n">
-        <v>461</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>920</v>
+        <v>840</v>
       </c>
       <c r="E152" t="n">
         <v>2</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
         <v>3</v>
@@ -3943,13 +3943,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>329</v>
+        <v>9</v>
       </c>
       <c r="C153" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>924</v>
+        <v>852</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -3966,19 +3966,19 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>849</v>
+        <v>7</v>
       </c>
       <c r="C154" t="n">
-        <v>851</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>967</v>
+        <v>853</v>
       </c>
       <c r="E154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
         <v>3</v>
@@ -3989,16 +3989,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="C155" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>971</v>
+        <v>864</v>
       </c>
       <c r="E155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -4012,19 +4012,19 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>253</v>
+        <v>7</v>
       </c>
       <c r="D156" t="n">
-        <v>975</v>
+        <v>901</v>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
         <v>3</v>
@@ -4035,19 +4035,19 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>575</v>
+        <v>1</v>
       </c>
       <c r="C157" t="n">
-        <v>540</v>
+        <v>4</v>
       </c>
       <c r="D157" t="n">
-        <v>979</v>
+        <v>920</v>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
         <v>3</v>
@@ -4058,19 +4058,19 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="D158" t="n">
-        <v>981</v>
+        <v>926</v>
       </c>
       <c r="E158" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
         <v>3</v>
@@ -4081,16 +4081,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>410</v>
+        <v>7</v>
       </c>
       <c r="D159" t="n">
-        <v>992</v>
+        <v>929</v>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -4104,16 +4104,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>461</v>
+        <v>1</v>
       </c>
       <c r="C160" t="n">
-        <v>607</v>
+        <v>7</v>
       </c>
       <c r="D160" t="n">
-        <v>997</v>
+        <v>967</v>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F160" t="n">
         <v>1</v>
@@ -4127,19 +4127,19 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>175</v>
+        <v>4</v>
       </c>
       <c r="D161" t="n">
-        <v>998</v>
+        <v>981</v>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
         <v>3</v>
@@ -4150,16 +4150,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="C162" t="n">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="D162" t="n">
-        <v>1037</v>
+        <v>987</v>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -4173,16 +4173,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="C163" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>1073</v>
+        <v>992</v>
       </c>
       <c r="E163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -4196,19 +4196,19 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>147</v>
+        <v>9</v>
       </c>
       <c r="C164" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>1089</v>
+        <v>997</v>
       </c>
       <c r="E164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164" t="n">
         <v>3</v>
@@ -4219,16 +4219,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>846</v>
+        <v>8</v>
       </c>
       <c r="C165" t="n">
-        <v>851</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>1103</v>
+        <v>1021</v>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -4242,19 +4242,19 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>217</v>
+        <v>2</v>
       </c>
       <c r="C166" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>1113</v>
+        <v>1037</v>
       </c>
       <c r="E166" t="n">
         <v>2</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
         <v>3</v>
@@ -4265,19 +4265,19 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>400</v>
+        <v>7</v>
       </c>
       <c r="C167" t="n">
-        <v>430</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1124</v>
+        <v>1057</v>
       </c>
       <c r="E167" t="n">
         <v>2</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
         <v>3</v>
@@ -4288,19 +4288,19 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>791</v>
+        <v>1</v>
       </c>
       <c r="C168" t="n">
-        <v>851</v>
+        <v>7</v>
       </c>
       <c r="D168" t="n">
-        <v>1132</v>
+        <v>1073</v>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
         <v>3</v>
@@ -4311,16 +4311,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>173</v>
+        <v>7</v>
       </c>
       <c r="C169" t="n">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>1155</v>
+        <v>1089</v>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -4334,19 +4334,19 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="C170" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>1155</v>
+        <v>1103</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
         <v>3</v>
@@ -4357,13 +4357,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>430</v>
+        <v>7</v>
       </c>
       <c r="C171" t="n">
-        <v>540</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1164</v>
+        <v>1124</v>
       </c>
       <c r="E171" t="n">
         <v>3</v>
@@ -4380,13 +4380,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>813</v>
+        <v>1</v>
       </c>
       <c r="C172" t="n">
-        <v>810</v>
+        <v>7</v>
       </c>
       <c r="D172" t="n">
-        <v>1193</v>
+        <v>1139</v>
       </c>
       <c r="E172" t="n">
         <v>2</v>
@@ -4403,13 +4403,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>185</v>
+        <v>3</v>
       </c>
       <c r="C173" t="n">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="D173" t="n">
-        <v>1203</v>
+        <v>1142</v>
       </c>
       <c r="E173" t="n">
         <v>1</v>
@@ -4426,19 +4426,19 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>607</v>
+        <v>3</v>
       </c>
       <c r="C174" t="n">
-        <v>766</v>
+        <v>5</v>
       </c>
       <c r="D174" t="n">
-        <v>1213</v>
+        <v>1146</v>
       </c>
       <c r="E174" t="n">
         <v>1</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" t="n">
         <v>3</v>
@@ -4449,16 +4449,16 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>630</v>
+        <v>1</v>
       </c>
       <c r="C175" t="n">
-        <v>510</v>
+        <v>7</v>
       </c>
       <c r="D175" t="n">
-        <v>1250</v>
+        <v>1155</v>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
@@ -4472,13 +4472,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>791</v>
+        <v>8</v>
       </c>
       <c r="C176" t="n">
-        <v>740</v>
+        <v>4</v>
       </c>
       <c r="D176" t="n">
-        <v>1251</v>
+        <v>1155</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -4495,19 +4495,19 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>621</v>
+        <v>2</v>
       </c>
       <c r="C177" t="n">
-        <v>630</v>
+        <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>1294</v>
+        <v>1164</v>
       </c>
       <c r="E177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>3</v>
@@ -4518,19 +4518,19 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>840</v>
+        <v>7</v>
       </c>
       <c r="C178" t="n">
-        <v>787</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>1294</v>
+        <v>1193</v>
       </c>
       <c r="E178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G178" t="n">
         <v>3</v>
@@ -4541,19 +4541,19 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>746</v>
+        <v>4</v>
       </c>
       <c r="C179" t="n">
-        <v>615</v>
+        <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>1303</v>
+        <v>1203</v>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" t="n">
         <v>3</v>
@@ -4564,16 +4564,16 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>326</v>
+        <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>376</v>
+        <v>7</v>
       </c>
       <c r="D180" t="n">
-        <v>1306</v>
+        <v>1213</v>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" t="n">
         <v>0</v>
@@ -4587,19 +4587,19 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>259</v>
+        <v>2</v>
       </c>
       <c r="C181" t="n">
-        <v>269</v>
+        <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>1308</v>
+        <v>1233</v>
       </c>
       <c r="E181" t="n">
         <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
         <v>3</v>
@@ -4610,22 +4610,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="D182" t="n">
-        <v>483</v>
+        <v>1250</v>
       </c>
       <c r="E182" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4633,22 +4633,22 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="D183" t="n">
-        <v>486</v>
+        <v>1251</v>
       </c>
       <c r="E183" t="n">
         <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4656,22 +4656,22 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="D184" t="n">
-        <v>489</v>
+        <v>1264</v>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4679,22 +4679,22 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="C185" t="n">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>494</v>
+        <v>1277</v>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4702,22 +4702,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>787</v>
+        <v>7</v>
       </c>
       <c r="C186" t="n">
-        <v>779</v>
+        <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>502</v>
+        <v>1285</v>
       </c>
       <c r="E186" t="n">
         <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -4725,22 +4725,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>510</v>
+        <v>8</v>
       </c>
       <c r="C187" t="n">
-        <v>746</v>
+        <v>7</v>
       </c>
       <c r="D187" t="n">
-        <v>568</v>
+        <v>1294</v>
       </c>
       <c r="E187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -4748,22 +4748,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>161</v>
+        <v>7</v>
       </c>
       <c r="C188" t="n">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>574</v>
+        <v>1294</v>
       </c>
       <c r="E188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -4771,22 +4771,22 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>219</v>
+        <v>7</v>
       </c>
       <c r="C189" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>605</v>
+        <v>1303</v>
       </c>
       <c r="E189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F189" t="n">
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -4794,22 +4794,22 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>707</v>
+        <v>1</v>
       </c>
       <c r="C190" t="n">
-        <v>706</v>
+        <v>2</v>
       </c>
       <c r="D190" t="n">
-        <v>611</v>
+        <v>1306</v>
       </c>
       <c r="E190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -4817,16 +4817,16 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="C191" t="n">
-        <v>306</v>
+        <v>4</v>
       </c>
       <c r="D191" t="n">
-        <v>618</v>
+        <v>483</v>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -4840,16 +4840,16 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>219</v>
+        <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>151</v>
+        <v>4</v>
       </c>
       <c r="D192" t="n">
-        <v>619</v>
+        <v>489</v>
       </c>
       <c r="E192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="C193" t="n">
-        <v>751</v>
+        <v>7</v>
       </c>
       <c r="D193" t="n">
-        <v>625</v>
+        <v>502</v>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -4886,16 +4886,16 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="C194" t="n">
-        <v>760</v>
+        <v>2</v>
       </c>
       <c r="D194" t="n">
-        <v>651</v>
+        <v>568</v>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F194" t="n">
         <v>1</v>
@@ -4909,19 +4909,19 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="C195" t="n">
-        <v>173</v>
+        <v>7</v>
       </c>
       <c r="D195" t="n">
-        <v>652</v>
+        <v>574</v>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
         <v>4</v>
@@ -4932,19 +4932,19 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="C196" t="n">
-        <v>185</v>
+        <v>7</v>
       </c>
       <c r="D196" t="n">
-        <v>695</v>
+        <v>576</v>
       </c>
       <c r="E196" t="n">
         <v>1</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
         <v>4</v>
@@ -4955,13 +4955,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>330</v>
+        <v>4</v>
       </c>
       <c r="C197" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>708</v>
+        <v>597</v>
       </c>
       <c r="E197" t="n">
         <v>1</v>
@@ -4978,19 +4978,19 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="C198" t="n">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>715</v>
+        <v>611</v>
       </c>
       <c r="E198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
         <v>4</v>
@@ -5001,19 +5001,19 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>210</v>
+        <v>4</v>
       </c>
       <c r="C199" t="n">
-        <v>217</v>
+        <v>5</v>
       </c>
       <c r="D199" t="n">
-        <v>722</v>
+        <v>612</v>
       </c>
       <c r="E199" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G199" t="n">
         <v>4</v>
@@ -5024,19 +5024,19 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>657</v>
+        <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>540</v>
+        <v>8</v>
       </c>
       <c r="D200" t="n">
-        <v>732</v>
+        <v>618</v>
       </c>
       <c r="E200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
         <v>4</v>
@@ -5047,19 +5047,19 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>167</v>
+        <v>9</v>
       </c>
       <c r="D201" t="n">
-        <v>736</v>
+        <v>619</v>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G201" t="n">
         <v>4</v>
@@ -5070,19 +5070,19 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>561</v>
+        <v>4</v>
       </c>
       <c r="C202" t="n">
-        <v>657</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>738</v>
+        <v>651</v>
       </c>
       <c r="E202" t="n">
         <v>1</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G202" t="n">
         <v>4</v>
@@ -5093,19 +5093,19 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>766</v>
+        <v>8</v>
       </c>
       <c r="C203" t="n">
-        <v>630</v>
+        <v>4</v>
       </c>
       <c r="D203" t="n">
-        <v>752</v>
+        <v>652</v>
       </c>
       <c r="E203" t="n">
         <v>1</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G203" t="n">
         <v>4</v>
@@ -5116,16 +5116,16 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>461</v>
+        <v>7</v>
       </c>
       <c r="C204" t="n">
-        <v>253</v>
+        <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>753</v>
+        <v>658</v>
       </c>
       <c r="E204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F204" t="n">
         <v>1</v>
@@ -5139,16 +5139,16 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="C205" t="n">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>756</v>
+        <v>677</v>
       </c>
       <c r="E205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F205" t="n">
         <v>1</v>
@@ -5162,13 +5162,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>265</v>
+        <v>4</v>
       </c>
       <c r="D206" t="n">
-        <v>761</v>
+        <v>708</v>
       </c>
       <c r="E206" t="n">
         <v>1</v>
@@ -5185,19 +5185,19 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>580</v>
+        <v>7</v>
       </c>
       <c r="C207" t="n">
-        <v>530</v>
+        <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>770</v>
+        <v>715</v>
       </c>
       <c r="E207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" t="n">
         <v>4</v>
@@ -5208,19 +5208,19 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="C208" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>774</v>
+        <v>722</v>
       </c>
       <c r="E208" t="n">
         <v>3</v>
       </c>
       <c r="F208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G208" t="n">
         <v>4</v>
@@ -5231,19 +5231,19 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="C209" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>775</v>
+        <v>738</v>
       </c>
       <c r="E209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G209" t="n">
         <v>4</v>
@@ -5254,16 +5254,16 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>791</v>
+        <v>7</v>
       </c>
       <c r="C210" t="n">
-        <v>661</v>
+        <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>794</v>
+        <v>740</v>
       </c>
       <c r="E210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -5277,13 +5277,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="C211" t="n">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="D211" t="n">
-        <v>801</v>
+        <v>756</v>
       </c>
       <c r="E211" t="n">
         <v>1</v>
@@ -5300,16 +5300,16 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>751</v>
+        <v>2</v>
       </c>
       <c r="C212" t="n">
-        <v>573</v>
+        <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>848</v>
+        <v>768</v>
       </c>
       <c r="E212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F212" t="n">
         <v>1</v>
@@ -5323,19 +5323,19 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="C213" t="n">
-        <v>185</v>
+        <v>2</v>
       </c>
       <c r="D213" t="n">
-        <v>855</v>
+        <v>768</v>
       </c>
       <c r="E213" t="n">
         <v>1</v>
       </c>
       <c r="F213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G213" t="n">
         <v>4</v>
@@ -5346,16 +5346,16 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>326</v>
+        <v>9</v>
       </c>
       <c r="C214" t="n">
-        <v>340</v>
+        <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>856</v>
+        <v>770</v>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F214" t="n">
         <v>0</v>
@@ -5369,16 +5369,16 @@
         <v>214</v>
       </c>
       <c r="B215" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="C215" t="n">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>858</v>
+        <v>774</v>
       </c>
       <c r="E215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F215" t="n">
         <v>1</v>
@@ -5392,19 +5392,19 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>671</v>
+        <v>1</v>
       </c>
       <c r="C216" t="n">
-        <v>370</v>
+        <v>2</v>
       </c>
       <c r="D216" t="n">
-        <v>873</v>
+        <v>775</v>
       </c>
       <c r="E216" t="n">
         <v>1</v>
       </c>
       <c r="F216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" t="n">
         <v>4</v>
@@ -5415,19 +5415,19 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>540</v>
+        <v>1</v>
       </c>
       <c r="C217" t="n">
-        <v>430</v>
+        <v>7</v>
       </c>
       <c r="D217" t="n">
-        <v>889</v>
+        <v>794</v>
       </c>
       <c r="E217" t="n">
         <v>1</v>
       </c>
       <c r="F217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G217" t="n">
         <v>4</v>
@@ -5438,19 +5438,19 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>813</v>
+        <v>4</v>
       </c>
       <c r="C218" t="n">
-        <v>860</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>904</v>
+        <v>799</v>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G218" t="n">
         <v>4</v>
@@ -5461,16 +5461,16 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>851</v>
+        <v>7</v>
       </c>
       <c r="C219" t="n">
-        <v>740</v>
+        <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>925</v>
+        <v>801</v>
       </c>
       <c r="E219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
         <v>1</v>
@@ -5484,13 +5484,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>510</v>
+        <v>10</v>
       </c>
       <c r="C220" t="n">
-        <v>561</v>
+        <v>8</v>
       </c>
       <c r="D220" t="n">
-        <v>949</v>
+        <v>825</v>
       </c>
       <c r="E220" t="n">
         <v>2</v>
@@ -5507,19 +5507,19 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>607</v>
+        <v>2</v>
       </c>
       <c r="C221" t="n">
-        <v>630</v>
+        <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>953</v>
+        <v>855</v>
       </c>
       <c r="E221" t="n">
         <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G221" t="n">
         <v>4</v>
@@ -5530,19 +5530,19 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>265</v>
+        <v>7</v>
       </c>
       <c r="C222" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>964</v>
+        <v>856</v>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
         <v>4</v>
@@ -5553,13 +5553,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>336</v>
+        <v>7</v>
       </c>
       <c r="C223" t="n">
-        <v>340</v>
+        <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>1004</v>
+        <v>858</v>
       </c>
       <c r="E223" t="n">
         <v>1</v>
@@ -5576,19 +5576,19 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>157</v>
+        <v>9</v>
       </c>
       <c r="C224" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="D224" t="n">
-        <v>1005</v>
+        <v>889</v>
       </c>
       <c r="E224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G224" t="n">
         <v>4</v>
@@ -5599,19 +5599,19 @@
         <v>224</v>
       </c>
       <c r="B225" t="n">
-        <v>530</v>
+        <v>1</v>
       </c>
       <c r="C225" t="n">
-        <v>575</v>
+        <v>7</v>
       </c>
       <c r="D225" t="n">
-        <v>1027</v>
+        <v>899</v>
       </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G225" t="n">
         <v>4</v>
@@ -5622,19 +5622,19 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="C226" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D226" t="n">
-        <v>1029</v>
+        <v>925</v>
       </c>
       <c r="E226" t="n">
         <v>3</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G226" t="n">
         <v>4</v>
@@ -5645,16 +5645,16 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="C227" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="D227" t="n">
-        <v>1053</v>
+        <v>979</v>
       </c>
       <c r="E227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -5668,19 +5668,19 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>270</v>
+        <v>7</v>
       </c>
       <c r="C228" t="n">
-        <v>219</v>
+        <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>1067</v>
+        <v>982</v>
       </c>
       <c r="E228" t="n">
         <v>3</v>
       </c>
       <c r="F228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G228" t="n">
         <v>4</v>
@@ -5691,16 +5691,16 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="C229" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="D229" t="n">
-        <v>1085</v>
+        <v>1027</v>
       </c>
       <c r="E229" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F229" t="n">
         <v>1</v>
@@ -5714,16 +5714,16 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="C230" t="n">
-        <v>730</v>
+        <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>1092</v>
+        <v>1029</v>
       </c>
       <c r="E230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F230" t="n">
         <v>0</v>
@@ -5737,16 +5737,16 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="C231" t="n">
-        <v>217</v>
+        <v>7</v>
       </c>
       <c r="D231" t="n">
-        <v>1103</v>
+        <v>1029</v>
       </c>
       <c r="E231" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F231" t="n">
         <v>1</v>
@@ -5760,19 +5760,19 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>510</v>
+        <v>1</v>
       </c>
       <c r="C232" t="n">
-        <v>540</v>
+        <v>7</v>
       </c>
       <c r="D232" t="n">
-        <v>1118</v>
+        <v>1053</v>
       </c>
       <c r="E232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G232" t="n">
         <v>4</v>
@@ -5783,19 +5783,19 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="C233" t="n">
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>1121</v>
+        <v>1067</v>
       </c>
       <c r="E233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
         <v>4</v>
@@ -5806,16 +5806,16 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>760</v>
+        <v>1</v>
       </c>
       <c r="C234" t="n">
-        <v>756</v>
+        <v>7</v>
       </c>
       <c r="D234" t="n">
-        <v>1133</v>
+        <v>1085</v>
       </c>
       <c r="E234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F234" t="n">
         <v>1</v>
@@ -5829,16 +5829,16 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>326</v>
+        <v>2</v>
       </c>
       <c r="C235" t="n">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>1143</v>
+        <v>1092</v>
       </c>
       <c r="E235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -5852,19 +5852,19 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C236" t="n">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="D236" t="n">
-        <v>1144</v>
+        <v>1095</v>
       </c>
       <c r="E236" t="n">
         <v>2</v>
       </c>
       <c r="F236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236" t="n">
         <v>4</v>
@@ -5875,13 +5875,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>751</v>
+        <v>9</v>
       </c>
       <c r="C237" t="n">
-        <v>740</v>
+        <v>3</v>
       </c>
       <c r="D237" t="n">
-        <v>1170</v>
+        <v>1102</v>
       </c>
       <c r="E237" t="n">
         <v>1</v>
@@ -5898,16 +5898,16 @@
         <v>237</v>
       </c>
       <c r="B238" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="C238" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="D238" t="n">
-        <v>1194</v>
+        <v>1103</v>
       </c>
       <c r="E238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -5921,16 +5921,16 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>163</v>
+        <v>6</v>
       </c>
       <c r="C239" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="D239" t="n">
-        <v>1203</v>
+        <v>1106</v>
       </c>
       <c r="E239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -5944,19 +5944,19 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>219</v>
+        <v>7</v>
       </c>
       <c r="C240" t="n">
-        <v>217</v>
+        <v>8</v>
       </c>
       <c r="D240" t="n">
-        <v>1229</v>
+        <v>1121</v>
       </c>
       <c r="E240" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G240" t="n">
         <v>4</v>
@@ -5967,19 +5967,19 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="C241" t="n">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="D241" t="n">
-        <v>1311</v>
+        <v>1133</v>
       </c>
       <c r="E241" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G241" t="n">
         <v>4</v>
@@ -5990,22 +5990,22 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>813</v>
+        <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>846</v>
+        <v>7</v>
       </c>
       <c r="D242" t="n">
-        <v>486</v>
+        <v>1139</v>
       </c>
       <c r="E242" t="n">
         <v>2</v>
       </c>
       <c r="F242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="243">
@@ -6013,22 +6013,22 @@
         <v>242</v>
       </c>
       <c r="B243" t="n">
-        <v>760</v>
+        <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>661</v>
+        <v>1</v>
       </c>
       <c r="D243" t="n">
-        <v>504</v>
+        <v>1143</v>
       </c>
       <c r="E243" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F243" t="n">
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="244">
@@ -6036,22 +6036,22 @@
         <v>243</v>
       </c>
       <c r="B244" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="C244" t="n">
-        <v>253</v>
+        <v>4</v>
       </c>
       <c r="D244" t="n">
-        <v>528</v>
+        <v>1144</v>
       </c>
       <c r="E244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245">
@@ -6059,22 +6059,22 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="C245" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D245" t="n">
-        <v>533</v>
+        <v>1164</v>
       </c>
       <c r="E245" t="n">
         <v>1</v>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246">
@@ -6082,22 +6082,22 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="D246" t="n">
-        <v>534</v>
+        <v>1170</v>
       </c>
       <c r="E246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="247">
@@ -6105,22 +6105,22 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>621</v>
+        <v>6</v>
       </c>
       <c r="C247" t="n">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="D247" t="n">
-        <v>534</v>
+        <v>1175</v>
       </c>
       <c r="E247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G247" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
@@ -6128,13 +6128,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="C248" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="D248" t="n">
-        <v>554</v>
+        <v>1194</v>
       </c>
       <c r="E248" t="n">
         <v>2</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249">
@@ -6151,22 +6151,22 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>773</v>
+        <v>8</v>
       </c>
       <c r="C249" t="n">
-        <v>710</v>
+        <v>7</v>
       </c>
       <c r="D249" t="n">
-        <v>567</v>
+        <v>1203</v>
       </c>
       <c r="E249" t="n">
         <v>2</v>
       </c>
       <c r="F249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G249" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="250">
@@ -6174,22 +6174,22 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>253</v>
+        <v>2</v>
       </c>
       <c r="C250" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D250" t="n">
-        <v>593</v>
+        <v>1273</v>
       </c>
       <c r="E250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="251">
@@ -6197,22 +6197,22 @@
         <v>250</v>
       </c>
       <c r="B251" t="n">
-        <v>430</v>
+        <v>8</v>
       </c>
       <c r="C251" t="n">
-        <v>540</v>
+        <v>4</v>
       </c>
       <c r="D251" t="n">
-        <v>594</v>
+        <v>1294</v>
       </c>
       <c r="E251" t="n">
         <v>1</v>
       </c>
       <c r="F251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G251" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252">
@@ -6220,22 +6220,22 @@
         <v>251</v>
       </c>
       <c r="B252" t="n">
-        <v>510</v>
+        <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>710</v>
+        <v>9</v>
       </c>
       <c r="D252" t="n">
-        <v>596</v>
+        <v>1311</v>
       </c>
       <c r="E252" t="n">
         <v>2</v>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253">
@@ -6243,22 +6243,22 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="D253" t="n">
-        <v>607</v>
+        <v>1313</v>
       </c>
       <c r="E253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
       </c>
       <c r="G253" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="254">
@@ -6266,16 +6266,16 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>810</v>
+        <v>1</v>
       </c>
       <c r="C254" t="n">
-        <v>820</v>
+        <v>7</v>
       </c>
       <c r="D254" t="n">
-        <v>616</v>
+        <v>486</v>
       </c>
       <c r="E254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -6289,19 +6289,19 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="C255" t="n">
-        <v>270</v>
+        <v>7</v>
       </c>
       <c r="D255" t="n">
-        <v>623</v>
+        <v>496</v>
       </c>
       <c r="E255" t="n">
         <v>1</v>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
         <v>5</v>
@@ -6312,19 +6312,19 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="C256" t="n">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="D256" t="n">
-        <v>630</v>
+        <v>518</v>
       </c>
       <c r="E256" t="n">
         <v>1</v>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G256" t="n">
         <v>5</v>
@@ -6335,19 +6335,19 @@
         <v>256</v>
       </c>
       <c r="B257" t="n">
-        <v>621</v>
+        <v>1</v>
       </c>
       <c r="C257" t="n">
-        <v>510</v>
+        <v>9</v>
       </c>
       <c r="D257" t="n">
-        <v>641</v>
+        <v>533</v>
       </c>
       <c r="E257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G257" t="n">
         <v>5</v>
@@ -6358,16 +6358,16 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>766</v>
+        <v>1</v>
       </c>
       <c r="C258" t="n">
-        <v>746</v>
+        <v>6</v>
       </c>
       <c r="D258" t="n">
-        <v>661</v>
+        <v>534</v>
       </c>
       <c r="E258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F258" t="n">
         <v>0</v>
@@ -6381,13 +6381,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="C259" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>673</v>
+        <v>534</v>
       </c>
       <c r="E259" t="n">
         <v>3</v>
@@ -6404,16 +6404,16 @@
         <v>259</v>
       </c>
       <c r="B260" t="n">
-        <v>706</v>
+        <v>7</v>
       </c>
       <c r="C260" t="n">
-        <v>751</v>
+        <v>1</v>
       </c>
       <c r="D260" t="n">
-        <v>689</v>
+        <v>534</v>
       </c>
       <c r="E260" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
@@ -6427,13 +6427,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>791</v>
+        <v>6</v>
       </c>
       <c r="C261" t="n">
-        <v>751</v>
+        <v>8</v>
       </c>
       <c r="D261" t="n">
-        <v>740</v>
+        <v>552</v>
       </c>
       <c r="E261" t="n">
         <v>1</v>
@@ -6450,16 +6450,16 @@
         <v>261</v>
       </c>
       <c r="B262" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="D262" t="n">
-        <v>743</v>
+        <v>567</v>
       </c>
       <c r="E262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F262" t="n">
         <v>1</v>
@@ -6473,19 +6473,19 @@
         <v>262</v>
       </c>
       <c r="B263" t="n">
-        <v>787</v>
+        <v>7</v>
       </c>
       <c r="C263" t="n">
-        <v>851</v>
+        <v>1</v>
       </c>
       <c r="D263" t="n">
-        <v>759</v>
+        <v>593</v>
       </c>
       <c r="E263" t="n">
         <v>2</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263" t="n">
         <v>5</v>
@@ -6496,16 +6496,16 @@
         <v>263</v>
       </c>
       <c r="B264" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="C264" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D264" t="n">
-        <v>764</v>
+        <v>594</v>
       </c>
       <c r="E264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
@@ -6519,19 +6519,19 @@
         <v>264</v>
       </c>
       <c r="B265" t="n">
-        <v>766</v>
+        <v>6</v>
       </c>
       <c r="C265" t="n">
-        <v>580</v>
+        <v>8</v>
       </c>
       <c r="D265" t="n">
-        <v>775</v>
+        <v>607</v>
       </c>
       <c r="E265" t="n">
         <v>2</v>
       </c>
       <c r="F265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G265" t="n">
         <v>5</v>
@@ -6542,19 +6542,19 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>730</v>
+        <v>2</v>
       </c>
       <c r="C266" t="n">
-        <v>710</v>
+        <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>784</v>
+        <v>609</v>
       </c>
       <c r="E266" t="n">
         <v>1</v>
       </c>
       <c r="F266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G266" t="n">
         <v>5</v>
@@ -6565,19 +6565,19 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>580</v>
+        <v>1</v>
       </c>
       <c r="C267" t="n">
-        <v>540</v>
+        <v>7</v>
       </c>
       <c r="D267" t="n">
-        <v>792</v>
+        <v>625</v>
       </c>
       <c r="E267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" t="n">
         <v>5</v>
@@ -6588,19 +6588,19 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>217</v>
+        <v>7</v>
       </c>
       <c r="C268" t="n">
-        <v>260</v>
+        <v>1</v>
       </c>
       <c r="D268" t="n">
-        <v>797</v>
+        <v>630</v>
       </c>
       <c r="E268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G268" t="n">
         <v>5</v>
@@ -6611,16 +6611,16 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C269" t="n">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="D269" t="n">
-        <v>821</v>
+        <v>641</v>
       </c>
       <c r="E269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F269" t="n">
         <v>1</v>
@@ -6634,19 +6634,19 @@
         <v>269</v>
       </c>
       <c r="B270" t="n">
-        <v>260</v>
+        <v>4</v>
       </c>
       <c r="C270" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="D270" t="n">
-        <v>838</v>
+        <v>673</v>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G270" t="n">
         <v>5</v>
@@ -6657,19 +6657,19 @@
         <v>270</v>
       </c>
       <c r="B271" t="n">
-        <v>430</v>
+        <v>7</v>
       </c>
       <c r="C271" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>839</v>
+        <v>680</v>
       </c>
       <c r="E271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G271" t="n">
         <v>5</v>
@@ -6680,19 +6680,19 @@
         <v>271</v>
       </c>
       <c r="B272" t="n">
-        <v>630</v>
+        <v>6</v>
       </c>
       <c r="C272" t="n">
-        <v>615</v>
+        <v>1</v>
       </c>
       <c r="D272" t="n">
-        <v>840</v>
+        <v>714</v>
       </c>
       <c r="E272" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G272" t="n">
         <v>5</v>
@@ -6703,13 +6703,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="n">
-        <v>450</v>
+        <v>7</v>
       </c>
       <c r="C273" t="n">
-        <v>461</v>
+        <v>1</v>
       </c>
       <c r="D273" t="n">
-        <v>860</v>
+        <v>740</v>
       </c>
       <c r="E273" t="n">
         <v>1</v>
@@ -6726,19 +6726,19 @@
         <v>273</v>
       </c>
       <c r="B274" t="n">
-        <v>540</v>
+        <v>7</v>
       </c>
       <c r="C274" t="n">
-        <v>430</v>
+        <v>1</v>
       </c>
       <c r="D274" t="n">
-        <v>870</v>
+        <v>743</v>
       </c>
       <c r="E274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274" t="n">
         <v>5</v>
@@ -6749,19 +6749,19 @@
         <v>274</v>
       </c>
       <c r="B275" t="n">
-        <v>376</v>
+        <v>8</v>
       </c>
       <c r="C275" t="n">
-        <v>360</v>
+        <v>4</v>
       </c>
       <c r="D275" t="n">
-        <v>884</v>
+        <v>759</v>
       </c>
       <c r="E275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G275" t="n">
         <v>5</v>
@@ -6772,19 +6772,19 @@
         <v>275</v>
       </c>
       <c r="B276" t="n">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="C276" t="n">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="D276" t="n">
-        <v>886</v>
+        <v>766</v>
       </c>
       <c r="E276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G276" t="n">
         <v>5</v>
@@ -6795,13 +6795,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="n">
-        <v>751</v>
+        <v>1</v>
       </c>
       <c r="C277" t="n">
-        <v>746</v>
+        <v>4</v>
       </c>
       <c r="D277" t="n">
-        <v>914</v>
+        <v>792</v>
       </c>
       <c r="E277" t="n">
         <v>1</v>
@@ -6818,13 +6818,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>376</v>
+        <v>1</v>
       </c>
       <c r="C278" t="n">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="D278" t="n">
-        <v>922</v>
+        <v>821</v>
       </c>
       <c r="E278" t="n">
         <v>1</v>
@@ -6841,13 +6841,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="n">
-        <v>751</v>
+        <v>7</v>
       </c>
       <c r="C279" t="n">
-        <v>730</v>
+        <v>1</v>
       </c>
       <c r="D279" t="n">
-        <v>950</v>
+        <v>835</v>
       </c>
       <c r="E279" t="n">
         <v>1</v>
@@ -6864,16 +6864,16 @@
         <v>279</v>
       </c>
       <c r="B280" t="n">
-        <v>253</v>
+        <v>1</v>
       </c>
       <c r="C280" t="n">
-        <v>169</v>
+        <v>7</v>
       </c>
       <c r="D280" t="n">
-        <v>979</v>
+        <v>838</v>
       </c>
       <c r="E280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F280" t="n">
         <v>0</v>
@@ -6887,13 +6887,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>580</v>
+        <v>1</v>
       </c>
       <c r="C281" t="n">
-        <v>730</v>
+        <v>7</v>
       </c>
       <c r="D281" t="n">
-        <v>979</v>
+        <v>850</v>
       </c>
       <c r="E281" t="n">
         <v>1</v>
@@ -6910,16 +6910,16 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="C282" t="n">
-        <v>580</v>
+        <v>7</v>
       </c>
       <c r="D282" t="n">
-        <v>980</v>
+        <v>857</v>
       </c>
       <c r="E282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F282" t="n">
         <v>1</v>
@@ -6933,19 +6933,19 @@
         <v>282</v>
       </c>
       <c r="B283" t="n">
-        <v>510</v>
+        <v>1</v>
       </c>
       <c r="C283" t="n">
-        <v>530</v>
+        <v>9</v>
       </c>
       <c r="D283" t="n">
-        <v>1008</v>
+        <v>860</v>
       </c>
       <c r="E283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G283" t="n">
         <v>5</v>
@@ -6956,19 +6956,19 @@
         <v>283</v>
       </c>
       <c r="B284" t="n">
-        <v>479</v>
+        <v>7</v>
       </c>
       <c r="C284" t="n">
-        <v>430</v>
+        <v>1</v>
       </c>
       <c r="D284" t="n">
-        <v>1031</v>
+        <v>870</v>
       </c>
       <c r="E284" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G284" t="n">
         <v>5</v>
@@ -6979,16 +6979,16 @@
         <v>284</v>
       </c>
       <c r="B285" t="n">
-        <v>217</v>
+        <v>2</v>
       </c>
       <c r="C285" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="D285" t="n">
-        <v>1054</v>
+        <v>880</v>
       </c>
       <c r="E285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F285" t="n">
         <v>1</v>
@@ -7002,16 +7002,16 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>219</v>
+        <v>1</v>
       </c>
       <c r="C286" t="n">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="D286" t="n">
-        <v>1058</v>
+        <v>885</v>
       </c>
       <c r="E286" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
@@ -7025,19 +7025,19 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>615</v>
+        <v>3</v>
       </c>
       <c r="C287" t="n">
-        <v>510</v>
+        <v>6</v>
       </c>
       <c r="D287" t="n">
-        <v>1111</v>
+        <v>914</v>
       </c>
       <c r="E287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G287" t="n">
         <v>5</v>
@@ -7048,16 +7048,16 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="C288" t="n">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="D288" t="n">
-        <v>1140</v>
+        <v>921</v>
       </c>
       <c r="E288" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
@@ -7071,19 +7071,19 @@
         <v>288</v>
       </c>
       <c r="B289" t="n">
-        <v>190</v>
+        <v>1</v>
       </c>
       <c r="C289" t="n">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="D289" t="n">
-        <v>1145</v>
+        <v>922</v>
       </c>
       <c r="E289" t="n">
         <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G289" t="n">
         <v>5</v>
@@ -7094,19 +7094,19 @@
         <v>289</v>
       </c>
       <c r="B290" t="n">
-        <v>330</v>
+        <v>4</v>
       </c>
       <c r="C290" t="n">
-        <v>329</v>
+        <v>1</v>
       </c>
       <c r="D290" t="n">
-        <v>1179</v>
+        <v>946</v>
       </c>
       <c r="E290" t="n">
         <v>2</v>
       </c>
       <c r="F290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G290" t="n">
         <v>5</v>
@@ -7117,16 +7117,16 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="C291" t="n">
-        <v>461</v>
+        <v>7</v>
       </c>
       <c r="D291" t="n">
-        <v>1213</v>
+        <v>950</v>
       </c>
       <c r="E291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F291" t="n">
         <v>0</v>
@@ -7140,16 +7140,16 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="C292" t="n">
-        <v>259</v>
+        <v>7</v>
       </c>
       <c r="D292" t="n">
-        <v>1214</v>
+        <v>979</v>
       </c>
       <c r="E292" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F292" t="n">
         <v>0</v>
@@ -7163,19 +7163,19 @@
         <v>292</v>
       </c>
       <c r="B293" t="n">
-        <v>657</v>
+        <v>8</v>
       </c>
       <c r="C293" t="n">
-        <v>751</v>
+        <v>1</v>
       </c>
       <c r="D293" t="n">
-        <v>1215</v>
+        <v>979</v>
       </c>
       <c r="E293" t="n">
         <v>1</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G293" t="n">
         <v>5</v>
@@ -7186,16 +7186,16 @@
         <v>293</v>
       </c>
       <c r="B294" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C294" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="D294" t="n">
-        <v>1225</v>
+        <v>986</v>
       </c>
       <c r="E294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
@@ -7209,19 +7209,19 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>370</v>
+        <v>7</v>
       </c>
       <c r="C295" t="n">
-        <v>320</v>
+        <v>1</v>
       </c>
       <c r="D295" t="n">
-        <v>1242</v>
+        <v>1031</v>
       </c>
       <c r="E295" t="n">
         <v>1</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G295" t="n">
         <v>5</v>
@@ -7232,19 +7232,19 @@
         <v>295</v>
       </c>
       <c r="B296" t="n">
-        <v>746</v>
+        <v>1</v>
       </c>
       <c r="C296" t="n">
-        <v>615</v>
+        <v>9</v>
       </c>
       <c r="D296" t="n">
-        <v>1248</v>
+        <v>1058</v>
       </c>
       <c r="E296" t="n">
         <v>2</v>
       </c>
       <c r="F296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G296" t="n">
         <v>5</v>
@@ -7255,13 +7255,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="n">
-        <v>169</v>
+        <v>7</v>
       </c>
       <c r="C297" t="n">
-        <v>260</v>
+        <v>8</v>
       </c>
       <c r="D297" t="n">
-        <v>1257</v>
+        <v>1089</v>
       </c>
       <c r="E297" t="n">
         <v>2</v>
@@ -7278,16 +7278,16 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>450</v>
+        <v>7</v>
       </c>
       <c r="C298" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="D298" t="n">
-        <v>1293</v>
+        <v>1111</v>
       </c>
       <c r="E298" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F298" t="n">
         <v>0</v>
@@ -7301,13 +7301,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="n">
-        <v>479</v>
+        <v>1</v>
       </c>
       <c r="C299" t="n">
-        <v>540</v>
+        <v>7</v>
       </c>
       <c r="D299" t="n">
-        <v>1294</v>
+        <v>1120</v>
       </c>
       <c r="E299" t="n">
         <v>2</v>
@@ -7324,19 +7324,19 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>510</v>
+        <v>1</v>
       </c>
       <c r="C300" t="n">
-        <v>580</v>
+        <v>7</v>
       </c>
       <c r="D300" t="n">
-        <v>1310</v>
+        <v>1155</v>
       </c>
       <c r="E300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G300" t="n">
         <v>5</v>
@@ -7347,21 +7347,366 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>706</v>
+        <v>7</v>
       </c>
       <c r="C301" t="n">
-        <v>851</v>
+        <v>1</v>
       </c>
       <c r="D301" t="n">
+        <v>1179</v>
+      </c>
+      <c r="E301" t="n">
+        <v>2</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1</v>
+      </c>
+      <c r="G301" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>7</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1181</v>
+      </c>
+      <c r="E302" t="n">
+        <v>2</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>1</v>
+      </c>
+      <c r="C303" t="n">
+        <v>9</v>
+      </c>
+      <c r="D303" t="n">
+        <v>1184</v>
+      </c>
+      <c r="E303" t="n">
+        <v>4</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>1</v>
+      </c>
+      <c r="C304" t="n">
+        <v>2</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>7</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1</v>
+      </c>
+      <c r="D305" t="n">
+        <v>1213</v>
+      </c>
+      <c r="E305" t="n">
+        <v>2</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>4</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1214</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>1</v>
+      </c>
+      <c r="C307" t="n">
+        <v>7</v>
+      </c>
+      <c r="D307" t="n">
+        <v>1223</v>
+      </c>
+      <c r="E307" t="n">
+        <v>3</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>1</v>
+      </c>
+      <c r="C308" t="n">
+        <v>4</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1225</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>8</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1</v>
+      </c>
+      <c r="D309" t="n">
+        <v>1241</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1</v>
+      </c>
+      <c r="F309" t="n">
+        <v>1</v>
+      </c>
+      <c r="G309" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>1</v>
+      </c>
+      <c r="C310" t="n">
+        <v>6</v>
+      </c>
+      <c r="D310" t="n">
+        <v>1257</v>
+      </c>
+      <c r="E310" t="n">
+        <v>2</v>
+      </c>
+      <c r="F310" t="n">
+        <v>1</v>
+      </c>
+      <c r="G310" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" t="n">
+        <v>7</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1258</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1</v>
+      </c>
+      <c r="F311" t="n">
+        <v>1</v>
+      </c>
+      <c r="G311" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>1</v>
+      </c>
+      <c r="C312" t="n">
+        <v>7</v>
+      </c>
+      <c r="D312" t="n">
+        <v>1293</v>
+      </c>
+      <c r="E312" t="n">
+        <v>2</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>4</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1294</v>
+      </c>
+      <c r="E313" t="n">
+        <v>3</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>5</v>
+      </c>
+      <c r="C314" t="n">
+        <v>3</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1296</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1</v>
+      </c>
+      <c r="F314" t="n">
+        <v>1</v>
+      </c>
+      <c r="G314" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>8</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>1</v>
+      </c>
+      <c r="C316" t="n">
+        <v>7</v>
+      </c>
+      <c r="D316" t="n">
         <v>1310</v>
       </c>
-      <c r="E301" t="n">
-        <v>1</v>
-      </c>
-      <c r="F301" t="n">
-        <v>1</v>
-      </c>
-      <c r="G301" t="n">
+      <c r="E316" t="n">
+        <v>2</v>
+      </c>
+      <c r="F316" t="n">
+        <v>1</v>
+      </c>
+      <c r="G316" t="n">
         <v>5</v>
       </c>
     </row>

--- a/DataGen/LTM/synthetic_demand_groups.xlsx
+++ b/DataGen/LTM/synthetic_demand_groups.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,19 +470,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -493,16 +493,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>488</v>
+        <v>515</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -516,19 +516,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>507</v>
+        <v>627</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -545,7 +545,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>515</v>
+        <v>630</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -562,16 +562,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>623</v>
+        <v>663</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>627</v>
+        <v>680</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -608,19 +608,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>630</v>
+        <v>696</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -631,19 +631,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>663</v>
+        <v>699</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -654,19 +654,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>680</v>
+        <v>704</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -683,13 +683,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -703,13 +703,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -723,13 +723,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>704</v>
+        <v>738</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -746,19 +746,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>704</v>
+        <v>773</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -769,16 +769,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>726</v>
+        <v>810</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>738</v>
+        <v>817</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -815,19 +815,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>773</v>
+        <v>825</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -838,19 +838,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -861,16 +861,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>817</v>
+        <v>890</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -884,16 +884,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>825</v>
+        <v>898</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -907,19 +907,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>827</v>
+        <v>921</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -936,10 +936,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>890</v>
+        <v>943</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -953,16 +953,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>898</v>
+        <v>968</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -976,19 +976,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>921</v>
+        <v>969</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -999,16 +999,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>943</v>
+        <v>972</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1025,10 +1025,10 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1045,16 +1045,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>969</v>
+        <v>982</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1068,16 +1068,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1091,19 +1091,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -1114,19 +1114,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>982</v>
+        <v>1000</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -1140,16 +1140,16 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>982</v>
+        <v>1030</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -1160,16 +1160,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>990</v>
+        <v>1033</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -1183,16 +1183,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>1000</v>
+        <v>1035</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -1206,19 +1206,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1030</v>
+        <v>1043</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -1235,10 +1235,10 @@
         <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>1033</v>
+        <v>1054</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -1252,16 +1252,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1035</v>
+        <v>1057</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -1275,19 +1275,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>1043</v>
+        <v>1089</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -1301,16 +1301,16 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>1054</v>
+        <v>1092</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -1321,13 +1321,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>1057</v>
+        <v>1112</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -1347,13 +1347,13 @@
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>1089</v>
+        <v>1117</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -1370,13 +1370,13 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>1092</v>
+        <v>1122</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1396,10 +1396,10 @@
         <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>1112</v>
+        <v>1125</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>1117</v>
+        <v>1127</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -1436,16 +1436,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1122</v>
+        <v>1143</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>1125</v>
+        <v>1151</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>1127</v>
+        <v>1171</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -1505,13 +1505,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>1143</v>
+        <v>1178</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -1528,19 +1528,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C48" t="n">
         <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>1151</v>
+        <v>1178</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -1554,10 +1554,10 @@
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>1171</v>
+        <v>1205</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
@@ -1574,19 +1574,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>1178</v>
+        <v>1209</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -1597,16 +1597,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>1178</v>
+        <v>1213</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1205</v>
+        <v>1215</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1643,19 +1643,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>1209</v>
+        <v>1218</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -1669,13 +1669,13 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>1213</v>
+        <v>1228</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1215</v>
+        <v>1243</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1715,16 +1715,16 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>1218</v>
+        <v>1258</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1738,16 +1738,16 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>1228</v>
+        <v>1259</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -1758,16 +1758,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1243</v>
+        <v>1274</v>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -1781,19 +1781,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>1258</v>
+        <v>1284</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -1807,13 +1807,13 @@
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>1259</v>
+        <v>1286</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -1827,13 +1827,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>1274</v>
+        <v>1292</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -1850,22 +1850,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D62" t="n">
-        <v>1284</v>
+        <v>484</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1873,22 +1873,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>1286</v>
+        <v>491</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -1896,13 +1896,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1292</v>
+        <v>497</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -1919,13 +1919,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -1948,13 +1948,13 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -1965,16 +1965,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -1988,16 +1988,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -2011,19 +2011,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>2</v>
@@ -2040,13 +2040,13 @@
         <v>7</v>
       </c>
       <c r="D70" t="n">
-        <v>532</v>
+        <v>565</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>2</v>
@@ -2063,10 +2063,10 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -2080,19 +2080,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="n">
         <v>8</v>
       </c>
-      <c r="C72" t="n">
-        <v>7</v>
-      </c>
       <c r="D72" t="n">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>2</v>
@@ -2103,19 +2103,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>2</v>
@@ -2126,13 +2126,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2149,19 +2149,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>583</v>
+        <v>622</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
         <v>2</v>
@@ -2172,13 +2172,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>597</v>
+        <v>640</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -2195,19 +2195,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>622</v>
+        <v>659</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>2</v>
@@ -2218,16 +2218,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D78" t="n">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -2241,16 +2241,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2264,16 +2264,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2287,16 +2287,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D81" t="n">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -2310,19 +2310,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D82" t="n">
-        <v>675</v>
+        <v>716</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>2</v>
@@ -2333,19 +2333,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D83" t="n">
-        <v>699</v>
+        <v>725</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
         <v>2</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>716</v>
+        <v>804</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2379,19 +2379,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>725</v>
+        <v>829</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>2</v>
@@ -2402,13 +2402,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>732</v>
+        <v>836</v>
       </c>
       <c r="E86" t="n">
         <v>2</v>
@@ -2425,19 +2425,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
+        <v>4</v>
+      </c>
+      <c r="C87" t="n">
         <v>8</v>
       </c>
-      <c r="C87" t="n">
-        <v>10</v>
-      </c>
       <c r="D87" t="n">
-        <v>756</v>
+        <v>923</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>2</v>
@@ -2448,19 +2448,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>804</v>
+        <v>932</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>2</v>
@@ -2477,13 +2477,13 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>829</v>
+        <v>953</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>2</v>
@@ -2500,13 +2500,13 @@
         <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>836</v>
+        <v>954</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
         <v>2</v>
@@ -2517,19 +2517,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>897</v>
+        <v>969</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
         <v>2</v>
@@ -2540,19 +2540,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D92" t="n">
-        <v>923</v>
+        <v>976</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
@@ -2566,13 +2566,13 @@
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D93" t="n">
-        <v>932</v>
+        <v>976</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -2586,16 +2586,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D94" t="n">
-        <v>953</v>
+        <v>1045</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -2612,10 +2612,10 @@
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D95" t="n">
-        <v>954</v>
+        <v>1049</v>
       </c>
       <c r="E95" t="n">
         <v>2</v>
@@ -2632,16 +2632,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>969</v>
+        <v>1060</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
@@ -2655,19 +2655,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>972</v>
+        <v>1083</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
         <v>2</v>
@@ -2678,19 +2678,19 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C98" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>976</v>
+        <v>1091</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
         <v>2</v>
@@ -2701,19 +2701,19 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1049</v>
+        <v>1115</v>
       </c>
       <c r="E99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
         <v>2</v>
@@ -2724,16 +2724,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1049</v>
+        <v>1120</v>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
@@ -2753,10 +2753,10 @@
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1060</v>
+        <v>1133</v>
       </c>
       <c r="E101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -2770,16 +2770,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D102" t="n">
-        <v>1083</v>
+        <v>1136</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
@@ -2793,16 +2793,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D103" t="n">
-        <v>1084</v>
+        <v>1138</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -2816,19 +2816,19 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C104" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1091</v>
+        <v>1142</v>
       </c>
       <c r="E104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
         <v>2</v>
@@ -2839,19 +2839,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D105" t="n">
-        <v>1115</v>
+        <v>1161</v>
       </c>
       <c r="E105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
         <v>2</v>
@@ -2865,13 +2865,13 @@
         <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
-        <v>1120</v>
+        <v>1161</v>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -2885,16 +2885,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>1133</v>
+        <v>1165</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
@@ -2911,16 +2911,16 @@
         <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>1136</v>
+        <v>1169</v>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>2</v>
@@ -2931,19 +2931,19 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D109" t="n">
-        <v>1138</v>
+        <v>1170</v>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
         <v>2</v>
@@ -2954,16 +2954,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D110" t="n">
-        <v>1142</v>
+        <v>1220</v>
       </c>
       <c r="E110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
@@ -2977,13 +2977,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>1161</v>
+        <v>1224</v>
       </c>
       <c r="E111" t="n">
         <v>2</v>
@@ -3000,16 +3000,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>1161</v>
+        <v>1230</v>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -3023,16 +3023,16 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D113" t="n">
-        <v>1169</v>
+        <v>1237</v>
       </c>
       <c r="E113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -3046,19 +3046,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C114" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>1170</v>
+        <v>1255</v>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" t="n">
         <v>2</v>
@@ -3075,10 +3075,10 @@
         <v>7</v>
       </c>
       <c r="D115" t="n">
-        <v>1206</v>
+        <v>1270</v>
       </c>
       <c r="E115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -3092,13 +3092,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>1220</v>
+        <v>1271</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3118,16 +3118,16 @@
         <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D117" t="n">
-        <v>1230</v>
+        <v>1279</v>
       </c>
       <c r="E117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
         <v>2</v>
@@ -3138,13 +3138,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>1237</v>
+        <v>1297</v>
       </c>
       <c r="E118" t="n">
         <v>1</v>
@@ -3161,16 +3161,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>1255</v>
+        <v>1299</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -3184,19 +3184,19 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C120" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>1270</v>
+        <v>1307</v>
       </c>
       <c r="E120" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
         <v>2</v>
@@ -3213,13 +3213,13 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>1271</v>
+        <v>1314</v>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>2</v>
@@ -3236,16 +3236,16 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>1271</v>
+        <v>480</v>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -3256,19 +3256,19 @@
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D123" t="n">
-        <v>1279</v>
+        <v>480</v>
       </c>
       <c r="E123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -3276,22 +3276,22 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D124" t="n">
-        <v>1297</v>
+        <v>484</v>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
@@ -3299,13 +3299,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>1299</v>
+        <v>491</v>
       </c>
       <c r="E125" t="n">
         <v>2</v>
@@ -3314,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -3322,22 +3322,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D126" t="n">
-        <v>1307</v>
+        <v>502</v>
       </c>
       <c r="E126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -3345,22 +3345,22 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D127" t="n">
-        <v>1314</v>
+        <v>518</v>
       </c>
       <c r="E127" t="n">
         <v>4</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -3368,19 +3368,19 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D128" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
         <v>3</v>
@@ -3391,19 +3391,19 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>484</v>
+        <v>533</v>
       </c>
       <c r="E129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>3</v>
@@ -3417,13 +3417,13 @@
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>491</v>
+        <v>537</v>
       </c>
       <c r="E130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -3437,19 +3437,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D131" t="n">
-        <v>502</v>
+        <v>549</v>
       </c>
       <c r="E131" t="n">
         <v>3</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
         <v>3</v>
@@ -3460,16 +3460,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>520</v>
+        <v>564</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -3483,16 +3483,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -3506,13 +3506,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C134" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D134" t="n">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -3529,19 +3529,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D135" t="n">
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
         <v>3</v>
@@ -3552,16 +3552,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>564</v>
+        <v>644</v>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F136" t="n">
         <v>1</v>
@@ -3575,19 +3575,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C137" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>574</v>
+        <v>649</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>3</v>
@@ -3598,19 +3598,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>596</v>
+        <v>669</v>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
         <v>3</v>
@@ -3621,19 +3621,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>617</v>
+        <v>692</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>3</v>
@@ -3644,16 +3644,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D140" t="n">
-        <v>645</v>
+        <v>696</v>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -3667,13 +3667,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>686</v>
+        <v>718</v>
       </c>
       <c r="E141" t="n">
         <v>1</v>
@@ -3693,16 +3693,16 @@
         <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>692</v>
+        <v>729</v>
       </c>
       <c r="E142" t="n">
         <v>1</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
         <v>3</v>
@@ -3713,19 +3713,19 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D143" t="n">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="E143" t="n">
         <v>2</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
         <v>3</v>
@@ -3736,19 +3736,19 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D144" t="n">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
         <v>3</v>
@@ -3765,10 +3765,10 @@
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>738</v>
+        <v>784</v>
       </c>
       <c r="E145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -3782,19 +3782,19 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C146" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>761</v>
+        <v>795</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
         <v>3</v>
@@ -3805,16 +3805,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>784</v>
+        <v>837</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F147" t="n">
         <v>1</v>
@@ -3828,19 +3828,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C148" t="n">
         <v>7</v>
       </c>
       <c r="D148" t="n">
-        <v>795</v>
+        <v>848</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
         <v>3</v>
@@ -3851,16 +3851,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D149" t="n">
-        <v>827</v>
+        <v>852</v>
       </c>
       <c r="E149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
@@ -3880,13 +3880,13 @@
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>837</v>
+        <v>853</v>
       </c>
       <c r="E150" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
         <v>3</v>
@@ -3897,13 +3897,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D151" t="n">
-        <v>839</v>
+        <v>864</v>
       </c>
       <c r="E151" t="n">
         <v>1</v>
@@ -3920,19 +3920,19 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>840</v>
+        <v>920</v>
       </c>
       <c r="E152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" t="n">
         <v>3</v>
@@ -3943,13 +3943,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D153" t="n">
-        <v>852</v>
+        <v>924</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -3972,13 +3972,13 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>853</v>
+        <v>967</v>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
         <v>3</v>
@@ -3989,16 +3989,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D155" t="n">
-        <v>864</v>
+        <v>971</v>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -4018,13 +4018,13 @@
         <v>7</v>
       </c>
       <c r="D156" t="n">
-        <v>901</v>
+        <v>975</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
         <v>3</v>
@@ -4035,19 +4035,19 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>920</v>
+        <v>979</v>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
         <v>3</v>
@@ -4064,13 +4064,13 @@
         <v>7</v>
       </c>
       <c r="D158" t="n">
-        <v>926</v>
+        <v>981</v>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
         <v>3</v>
@@ -4081,16 +4081,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>929</v>
+        <v>992</v>
       </c>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -4104,16 +4104,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>967</v>
+        <v>997</v>
       </c>
       <c r="E160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F160" t="n">
         <v>1</v>
@@ -4130,16 +4130,16 @@
         <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>981</v>
+        <v>998</v>
       </c>
       <c r="E161" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161" t="n">
         <v>3</v>
@@ -4153,10 +4153,10 @@
         <v>1</v>
       </c>
       <c r="C162" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>987</v>
+        <v>1037</v>
       </c>
       <c r="E162" t="n">
         <v>2</v>
@@ -4173,16 +4173,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>992</v>
+        <v>1073</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -4196,19 +4196,19 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>997</v>
+        <v>1089</v>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
         <v>3</v>
@@ -4219,13 +4219,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>1021</v>
+        <v>1103</v>
       </c>
       <c r="E165" t="n">
         <v>2</v>
@@ -4242,19 +4242,19 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D166" t="n">
-        <v>1037</v>
+        <v>1113</v>
       </c>
       <c r="E166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
         <v>3</v>
@@ -4265,19 +4265,19 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1057</v>
+        <v>1124</v>
       </c>
       <c r="E167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
         <v>3</v>
@@ -4288,19 +4288,19 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C168" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>1073</v>
+        <v>1132</v>
       </c>
       <c r="E168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" t="n">
         <v>3</v>
@@ -4311,16 +4311,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D169" t="n">
-        <v>1089</v>
+        <v>1155</v>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -4334,19 +4334,19 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D170" t="n">
-        <v>1103</v>
+        <v>1155</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G170" t="n">
         <v>3</v>
@@ -4357,16 +4357,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1124</v>
+        <v>1164</v>
       </c>
       <c r="E171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F171" t="n">
         <v>1</v>
@@ -4380,16 +4380,16 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C172" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>1139</v>
+        <v>1193</v>
       </c>
       <c r="E172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
@@ -4403,16 +4403,16 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D173" t="n">
-        <v>1142</v>
+        <v>1203</v>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -4426,19 +4426,19 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C174" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>1146</v>
+        <v>1213</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
         <v>3</v>
@@ -4449,16 +4449,16 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C175" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>1155</v>
+        <v>1250</v>
       </c>
       <c r="E175" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
@@ -4472,13 +4472,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C176" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>1155</v>
+        <v>1251</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -4495,19 +4495,19 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D177" t="n">
-        <v>1164</v>
+        <v>1294</v>
       </c>
       <c r="E177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
         <v>3</v>
@@ -4524,13 +4524,13 @@
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>1193</v>
+        <v>1294</v>
       </c>
       <c r="E178" t="n">
         <v>3</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
         <v>3</v>
@@ -4541,19 +4541,19 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>1203</v>
+        <v>1303</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
         <v>3</v>
@@ -4564,16 +4564,16 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C180" t="n">
         <v>7</v>
       </c>
       <c r="D180" t="n">
-        <v>1213</v>
+        <v>1306</v>
       </c>
       <c r="E180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F180" t="n">
         <v>0</v>
@@ -4587,19 +4587,19 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D181" t="n">
-        <v>1233</v>
+        <v>1308</v>
       </c>
       <c r="E181" t="n">
         <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
         <v>3</v>
@@ -4613,19 +4613,19 @@
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D182" t="n">
-        <v>1250</v>
+        <v>483</v>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
@@ -4636,19 +4636,19 @@
         <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D183" t="n">
-        <v>1251</v>
+        <v>486</v>
       </c>
       <c r="E183" t="n">
         <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184">
@@ -4659,19 +4659,19 @@
         <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D184" t="n">
-        <v>1264</v>
+        <v>489</v>
       </c>
       <c r="E184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185">
@@ -4679,22 +4679,22 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D185" t="n">
-        <v>1277</v>
+        <v>494</v>
       </c>
       <c r="E185" t="n">
         <v>2</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186">
@@ -4708,16 +4708,16 @@
         <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>1285</v>
+        <v>502</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187">
@@ -4725,22 +4725,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C187" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>1294</v>
+        <v>568</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
@@ -4748,22 +4748,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D188" t="n">
-        <v>1294</v>
+        <v>574</v>
       </c>
       <c r="E188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189">
@@ -4771,22 +4771,22 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D189" t="n">
-        <v>1303</v>
+        <v>605</v>
       </c>
       <c r="E189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
         <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190">
@@ -4794,22 +4794,22 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>1306</v>
+        <v>611</v>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191">
@@ -4817,16 +4817,16 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C191" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D191" t="n">
-        <v>483</v>
+        <v>618</v>
       </c>
       <c r="E191" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -4843,13 +4843,13 @@
         <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D192" t="n">
-        <v>489</v>
+        <v>619</v>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
         <v>7</v>
       </c>
       <c r="D193" t="n">
-        <v>502</v>
+        <v>625</v>
       </c>
       <c r="E193" t="n">
         <v>2</v>
@@ -4889,13 +4889,13 @@
         <v>1</v>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D194" t="n">
-        <v>568</v>
+        <v>651</v>
       </c>
       <c r="E194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F194" t="n">
         <v>1</v>
@@ -4912,16 +4912,16 @@
         <v>1</v>
       </c>
       <c r="C195" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D195" t="n">
-        <v>574</v>
+        <v>652</v>
       </c>
       <c r="E195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195" t="n">
         <v>4</v>
@@ -4938,13 +4938,13 @@
         <v>7</v>
       </c>
       <c r="D196" t="n">
-        <v>576</v>
+        <v>695</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G196" t="n">
         <v>4</v>
@@ -4955,13 +4955,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D197" t="n">
-        <v>597</v>
+        <v>708</v>
       </c>
       <c r="E197" t="n">
         <v>1</v>
@@ -4978,19 +4978,19 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>611</v>
+        <v>715</v>
       </c>
       <c r="E198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G198" t="n">
         <v>4</v>
@@ -5001,19 +5001,19 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C199" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D199" t="n">
-        <v>612</v>
+        <v>722</v>
       </c>
       <c r="E199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
         <v>4</v>
@@ -5024,19 +5024,19 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C200" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>618</v>
+        <v>732</v>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
         <v>4</v>
@@ -5050,16 +5050,16 @@
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D201" t="n">
-        <v>619</v>
+        <v>736</v>
       </c>
       <c r="E201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G201" t="n">
         <v>4</v>
@@ -5070,19 +5070,19 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>651</v>
+        <v>738</v>
       </c>
       <c r="E202" t="n">
         <v>1</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
         <v>4</v>
@@ -5093,19 +5093,19 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C203" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>652</v>
+        <v>752</v>
       </c>
       <c r="E203" t="n">
         <v>1</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
         <v>4</v>
@@ -5116,13 +5116,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>658</v>
+        <v>753</v>
       </c>
       <c r="E204" t="n">
         <v>2</v>
@@ -5139,16 +5139,16 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D205" t="n">
-        <v>677</v>
+        <v>756</v>
       </c>
       <c r="E205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F205" t="n">
         <v>1</v>
@@ -5165,10 +5165,10 @@
         <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D206" t="n">
-        <v>708</v>
+        <v>761</v>
       </c>
       <c r="E206" t="n">
         <v>1</v>
@@ -5185,19 +5185,19 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>715</v>
+        <v>770</v>
       </c>
       <c r="E207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G207" t="n">
         <v>4</v>
@@ -5208,19 +5208,19 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D208" t="n">
-        <v>722</v>
+        <v>774</v>
       </c>
       <c r="E208" t="n">
         <v>3</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208" t="n">
         <v>4</v>
@@ -5231,19 +5231,19 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D209" t="n">
-        <v>738</v>
+        <v>775</v>
       </c>
       <c r="E209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G209" t="n">
         <v>4</v>
@@ -5260,10 +5260,10 @@
         <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>740</v>
+        <v>794</v>
       </c>
       <c r="E210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -5283,7 +5283,7 @@
         <v>7</v>
       </c>
       <c r="D211" t="n">
-        <v>756</v>
+        <v>801</v>
       </c>
       <c r="E211" t="n">
         <v>1</v>
@@ -5300,16 +5300,16 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>768</v>
+        <v>848</v>
       </c>
       <c r="E212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F212" t="n">
         <v>1</v>
@@ -5323,19 +5323,19 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D213" t="n">
-        <v>768</v>
+        <v>855</v>
       </c>
       <c r="E213" t="n">
         <v>1</v>
       </c>
       <c r="F213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G213" t="n">
         <v>4</v>
@@ -5346,16 +5346,16 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C214" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D214" t="n">
-        <v>770</v>
+        <v>856</v>
       </c>
       <c r="E214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F214" t="n">
         <v>0</v>
@@ -5369,16 +5369,16 @@
         <v>214</v>
       </c>
       <c r="B215" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D215" t="n">
-        <v>774</v>
+        <v>858</v>
       </c>
       <c r="E215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F215" t="n">
         <v>1</v>
@@ -5392,19 +5392,19 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216" t="n">
-        <v>775</v>
+        <v>873</v>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G216" t="n">
         <v>4</v>
@@ -5415,19 +5415,19 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C217" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>794</v>
+        <v>889</v>
       </c>
       <c r="E217" t="n">
         <v>1</v>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G217" t="n">
         <v>4</v>
@@ -5438,19 +5438,19 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>799</v>
+        <v>904</v>
       </c>
       <c r="E218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
         <v>4</v>
@@ -5464,13 +5464,13 @@
         <v>7</v>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D219" t="n">
-        <v>801</v>
+        <v>925</v>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F219" t="n">
         <v>1</v>
@@ -5484,13 +5484,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C220" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>825</v>
+        <v>949</v>
       </c>
       <c r="E220" t="n">
         <v>2</v>
@@ -5507,19 +5507,19 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>855</v>
+        <v>953</v>
       </c>
       <c r="E221" t="n">
         <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G221" t="n">
         <v>4</v>
@@ -5530,19 +5530,19 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D222" t="n">
-        <v>856</v>
+        <v>964</v>
       </c>
       <c r="E222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G222" t="n">
         <v>4</v>
@@ -5553,13 +5553,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D223" t="n">
-        <v>858</v>
+        <v>1004</v>
       </c>
       <c r="E223" t="n">
         <v>1</v>
@@ -5576,19 +5576,19 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D224" t="n">
-        <v>889</v>
+        <v>1005</v>
       </c>
       <c r="E224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G224" t="n">
         <v>4</v>
@@ -5599,19 +5599,19 @@
         <v>224</v>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C225" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D225" t="n">
-        <v>899</v>
+        <v>1027</v>
       </c>
       <c r="E225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G225" t="n">
         <v>4</v>
@@ -5625,16 +5625,16 @@
         <v>1</v>
       </c>
       <c r="C226" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D226" t="n">
-        <v>925</v>
+        <v>1029</v>
       </c>
       <c r="E226" t="n">
         <v>3</v>
       </c>
       <c r="F226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G226" t="n">
         <v>4</v>
@@ -5651,7 +5651,7 @@
         <v>4</v>
       </c>
       <c r="D227" t="n">
-        <v>979</v>
+        <v>1053</v>
       </c>
       <c r="E227" t="n">
         <v>2</v>
@@ -5668,19 +5668,19 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>982</v>
+        <v>1067</v>
       </c>
       <c r="E228" t="n">
         <v>3</v>
       </c>
       <c r="F228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G228" t="n">
         <v>4</v>
@@ -5694,13 +5694,13 @@
         <v>1</v>
       </c>
       <c r="C229" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D229" t="n">
-        <v>1027</v>
+        <v>1085</v>
       </c>
       <c r="E229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F229" t="n">
         <v>1</v>
@@ -5714,16 +5714,16 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D230" t="n">
-        <v>1029</v>
+        <v>1092</v>
       </c>
       <c r="E230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F230" t="n">
         <v>0</v>
@@ -5737,16 +5737,16 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C231" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>1029</v>
+        <v>1103</v>
       </c>
       <c r="E231" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F231" t="n">
         <v>1</v>
@@ -5760,19 +5760,19 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C232" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D232" t="n">
-        <v>1053</v>
+        <v>1118</v>
       </c>
       <c r="E232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" t="n">
         <v>4</v>
@@ -5783,19 +5783,19 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233" t="n">
-        <v>1067</v>
+        <v>1121</v>
       </c>
       <c r="E233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
         <v>4</v>
@@ -5806,13 +5806,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C234" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>1085</v>
+        <v>1133</v>
       </c>
       <c r="E234" t="n">
         <v>3</v>
@@ -5829,16 +5829,16 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D235" t="n">
-        <v>1092</v>
+        <v>1143</v>
       </c>
       <c r="E235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -5855,16 +5855,16 @@
         <v>1</v>
       </c>
       <c r="C236" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D236" t="n">
-        <v>1095</v>
+        <v>1144</v>
       </c>
       <c r="E236" t="n">
         <v>2</v>
       </c>
       <c r="F236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G236" t="n">
         <v>4</v>
@@ -5875,16 +5875,16 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D237" t="n">
-        <v>1102</v>
+        <v>1170</v>
       </c>
       <c r="E237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
@@ -5901,10 +5901,10 @@
         <v>1</v>
       </c>
       <c r="C238" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D238" t="n">
-        <v>1103</v>
+        <v>1194</v>
       </c>
       <c r="E238" t="n">
         <v>2</v>
@@ -5921,16 +5921,16 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C239" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D239" t="n">
-        <v>1106</v>
+        <v>1203</v>
       </c>
       <c r="E239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -5944,19 +5944,19 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C240" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D240" t="n">
-        <v>1121</v>
+        <v>1229</v>
       </c>
       <c r="E240" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G240" t="n">
         <v>4</v>
@@ -5973,13 +5973,13 @@
         <v>7</v>
       </c>
       <c r="D241" t="n">
-        <v>1133</v>
+        <v>1311</v>
       </c>
       <c r="E241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G241" t="n">
         <v>4</v>
@@ -5990,22 +5990,22 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C242" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D242" t="n">
-        <v>1139</v>
+        <v>486</v>
       </c>
       <c r="E242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243">
@@ -6013,22 +6013,22 @@
         <v>242</v>
       </c>
       <c r="B243" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
       </c>
       <c r="D243" t="n">
-        <v>1143</v>
+        <v>504</v>
       </c>
       <c r="E243" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F243" t="n">
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244">
@@ -6039,19 +6039,19 @@
         <v>1</v>
       </c>
       <c r="C244" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D244" t="n">
-        <v>1144</v>
+        <v>528</v>
       </c>
       <c r="E244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245">
@@ -6059,22 +6059,22 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D245" t="n">
-        <v>1164</v>
+        <v>533</v>
       </c>
       <c r="E245" t="n">
         <v>1</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246">
@@ -6085,19 +6085,19 @@
         <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D246" t="n">
-        <v>1170</v>
+        <v>534</v>
       </c>
       <c r="E246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247">
@@ -6105,22 +6105,22 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
       </c>
       <c r="D247" t="n">
-        <v>1175</v>
+        <v>534</v>
       </c>
       <c r="E247" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248">
@@ -6134,7 +6134,7 @@
         <v>4</v>
       </c>
       <c r="D248" t="n">
-        <v>1194</v>
+        <v>554</v>
       </c>
       <c r="E248" t="n">
         <v>2</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249">
@@ -6151,22 +6151,22 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C249" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D249" t="n">
-        <v>1203</v>
+        <v>567</v>
       </c>
       <c r="E249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250">
@@ -6174,22 +6174,22 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D250" t="n">
-        <v>1273</v>
+        <v>593</v>
       </c>
       <c r="E250" t="n">
         <v>2</v>
       </c>
       <c r="F250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G250" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251">
@@ -6197,22 +6197,22 @@
         <v>250</v>
       </c>
       <c r="B251" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C251" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D251" t="n">
-        <v>1294</v>
+        <v>594</v>
       </c>
       <c r="E251" t="n">
         <v>1</v>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252">
@@ -6220,22 +6220,22 @@
         <v>251</v>
       </c>
       <c r="B252" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C252" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D252" t="n">
-        <v>1311</v>
+        <v>596</v>
       </c>
       <c r="E252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253">
@@ -6246,19 +6246,19 @@
         <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D253" t="n">
-        <v>1313</v>
+        <v>607</v>
       </c>
       <c r="E253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
       </c>
       <c r="G253" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254">
@@ -6266,16 +6266,16 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C254" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D254" t="n">
-        <v>486</v>
+        <v>616</v>
       </c>
       <c r="E254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -6292,16 +6292,16 @@
         <v>1</v>
       </c>
       <c r="C255" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D255" t="n">
-        <v>496</v>
+        <v>623</v>
       </c>
       <c r="E255" t="n">
         <v>1</v>
       </c>
       <c r="F255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G255" t="n">
         <v>5</v>
@@ -6312,19 +6312,19 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D256" t="n">
-        <v>518</v>
+        <v>630</v>
       </c>
       <c r="E256" t="n">
         <v>1</v>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G256" t="n">
         <v>5</v>
@@ -6335,19 +6335,19 @@
         <v>256</v>
       </c>
       <c r="B257" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C257" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D257" t="n">
-        <v>533</v>
+        <v>641</v>
       </c>
       <c r="E257" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G257" t="n">
         <v>5</v>
@@ -6358,16 +6358,16 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C258" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D258" t="n">
-        <v>534</v>
+        <v>661</v>
       </c>
       <c r="E258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F258" t="n">
         <v>0</v>
@@ -6381,16 +6381,16 @@
         <v>258</v>
       </c>
       <c r="B259" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D259" t="n">
-        <v>534</v>
+        <v>673</v>
       </c>
       <c r="E259" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -6410,10 +6410,10 @@
         <v>1</v>
       </c>
       <c r="D260" t="n">
-        <v>534</v>
+        <v>689</v>
       </c>
       <c r="E260" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
@@ -6427,13 +6427,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C261" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D261" t="n">
-        <v>552</v>
+        <v>740</v>
       </c>
       <c r="E261" t="n">
         <v>1</v>
@@ -6453,13 +6453,13 @@
         <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D262" t="n">
-        <v>567</v>
+        <v>743</v>
       </c>
       <c r="E262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F262" t="n">
         <v>1</v>
@@ -6479,13 +6479,13 @@
         <v>1</v>
       </c>
       <c r="D263" t="n">
-        <v>593</v>
+        <v>759</v>
       </c>
       <c r="E263" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G263" t="n">
         <v>5</v>
@@ -6499,10 +6499,10 @@
         <v>1</v>
       </c>
       <c r="C264" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D264" t="n">
-        <v>594</v>
+        <v>764</v>
       </c>
       <c r="E264" t="n">
         <v>1</v>
@@ -6519,19 +6519,19 @@
         <v>264</v>
       </c>
       <c r="B265" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C265" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D265" t="n">
-        <v>607</v>
+        <v>775</v>
       </c>
       <c r="E265" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G265" t="n">
         <v>5</v>
@@ -6542,19 +6542,19 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C266" t="n">
         <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>609</v>
+        <v>784</v>
       </c>
       <c r="E266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G266" t="n">
         <v>5</v>
@@ -6565,19 +6565,19 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C267" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>625</v>
+        <v>792</v>
       </c>
       <c r="E267" t="n">
         <v>1</v>
       </c>
       <c r="F267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" t="n">
         <v>5</v>
@@ -6588,19 +6588,19 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C268" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D268" t="n">
-        <v>630</v>
+        <v>797</v>
       </c>
       <c r="E268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G268" t="n">
         <v>5</v>
@@ -6614,13 +6614,13 @@
         <v>1</v>
       </c>
       <c r="C269" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D269" t="n">
-        <v>641</v>
+        <v>821</v>
       </c>
       <c r="E269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F269" t="n">
         <v>1</v>
@@ -6634,19 +6634,19 @@
         <v>269</v>
       </c>
       <c r="B270" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D270" t="n">
-        <v>673</v>
+        <v>838</v>
       </c>
       <c r="E270" t="n">
         <v>2</v>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
         <v>5</v>
@@ -6657,19 +6657,19 @@
         <v>270</v>
       </c>
       <c r="B271" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C271" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D271" t="n">
-        <v>680</v>
+        <v>839</v>
       </c>
       <c r="E271" t="n">
         <v>1</v>
       </c>
       <c r="F271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G271" t="n">
         <v>5</v>
@@ -6680,19 +6680,19 @@
         <v>271</v>
       </c>
       <c r="B272" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C272" t="n">
         <v>1</v>
       </c>
       <c r="D272" t="n">
-        <v>714</v>
+        <v>840</v>
       </c>
       <c r="E272" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G272" t="n">
         <v>5</v>
@@ -6703,13 +6703,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D273" t="n">
-        <v>740</v>
+        <v>860</v>
       </c>
       <c r="E273" t="n">
         <v>1</v>
@@ -6726,19 +6726,19 @@
         <v>273</v>
       </c>
       <c r="B274" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C274" t="n">
         <v>1</v>
       </c>
       <c r="D274" t="n">
-        <v>743</v>
+        <v>870</v>
       </c>
       <c r="E274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
         <v>5</v>
@@ -6749,19 +6749,19 @@
         <v>274</v>
       </c>
       <c r="B275" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C275" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D275" t="n">
-        <v>759</v>
+        <v>884</v>
       </c>
       <c r="E275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G275" t="n">
         <v>5</v>
@@ -6772,19 +6772,19 @@
         <v>275</v>
       </c>
       <c r="B276" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C276" t="n">
         <v>7</v>
       </c>
       <c r="D276" t="n">
-        <v>766</v>
+        <v>886</v>
       </c>
       <c r="E276" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G276" t="n">
         <v>5</v>
@@ -6795,16 +6795,16 @@
         <v>276</v>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C277" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D277" t="n">
-        <v>792</v>
+        <v>914</v>
       </c>
       <c r="E277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F277" t="n">
         <v>0</v>
@@ -6818,13 +6818,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C278" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D278" t="n">
-        <v>821</v>
+        <v>922</v>
       </c>
       <c r="E278" t="n">
         <v>1</v>
@@ -6847,10 +6847,10 @@
         <v>1</v>
       </c>
       <c r="D279" t="n">
-        <v>835</v>
+        <v>950</v>
       </c>
       <c r="E279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
@@ -6870,10 +6870,10 @@
         <v>7</v>
       </c>
       <c r="D280" t="n">
-        <v>838</v>
+        <v>979</v>
       </c>
       <c r="E280" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F280" t="n">
         <v>0</v>
@@ -6887,13 +6887,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C281" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D281" t="n">
-        <v>850</v>
+        <v>979</v>
       </c>
       <c r="E281" t="n">
         <v>1</v>
@@ -6910,16 +6910,16 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C282" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D282" t="n">
-        <v>857</v>
+        <v>980</v>
       </c>
       <c r="E282" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F282" t="n">
         <v>1</v>
@@ -6933,19 +6933,19 @@
         <v>282</v>
       </c>
       <c r="B283" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C283" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D283" t="n">
-        <v>860</v>
+        <v>1008</v>
       </c>
       <c r="E283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G283" t="n">
         <v>5</v>
@@ -6956,19 +6956,19 @@
         <v>283</v>
       </c>
       <c r="B284" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C284" t="n">
         <v>1</v>
       </c>
       <c r="D284" t="n">
-        <v>870</v>
+        <v>1031</v>
       </c>
       <c r="E284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G284" t="n">
         <v>5</v>
@@ -6979,13 +6979,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C285" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D285" t="n">
-        <v>880</v>
+        <v>1054</v>
       </c>
       <c r="E285" t="n">
         <v>2</v>
@@ -7008,10 +7008,10 @@
         <v>7</v>
       </c>
       <c r="D286" t="n">
-        <v>885</v>
+        <v>1058</v>
       </c>
       <c r="E286" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
@@ -7025,19 +7025,19 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C287" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D287" t="n">
-        <v>914</v>
+        <v>1111</v>
       </c>
       <c r="E287" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G287" t="n">
         <v>5</v>
@@ -7051,13 +7051,13 @@
         <v>1</v>
       </c>
       <c r="C288" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D288" t="n">
-        <v>921</v>
+        <v>1140</v>
       </c>
       <c r="E288" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>7</v>
       </c>
       <c r="D289" t="n">
-        <v>922</v>
+        <v>1145</v>
       </c>
       <c r="E289" t="n">
         <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289" t="n">
         <v>5</v>
@@ -7094,19 +7094,19 @@
         <v>289</v>
       </c>
       <c r="B290" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C290" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D290" t="n">
-        <v>946</v>
+        <v>1179</v>
       </c>
       <c r="E290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G290" t="n">
         <v>5</v>
@@ -7117,16 +7117,16 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C291" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D291" t="n">
-        <v>950</v>
+        <v>1213</v>
       </c>
       <c r="E291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F291" t="n">
         <v>0</v>
@@ -7140,16 +7140,16 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C292" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D292" t="n">
-        <v>979</v>
+        <v>1214</v>
       </c>
       <c r="E292" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F292" t="n">
         <v>0</v>
@@ -7163,19 +7163,19 @@
         <v>292</v>
       </c>
       <c r="B293" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C293" t="n">
         <v>1</v>
       </c>
       <c r="D293" t="n">
-        <v>979</v>
+        <v>1215</v>
       </c>
       <c r="E293" t="n">
         <v>1</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G293" t="n">
         <v>5</v>
@@ -7189,13 +7189,13 @@
         <v>1</v>
       </c>
       <c r="C294" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D294" t="n">
-        <v>986</v>
+        <v>1225</v>
       </c>
       <c r="E294" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
@@ -7209,19 +7209,19 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C295" t="n">
         <v>1</v>
       </c>
       <c r="D295" t="n">
-        <v>1031</v>
+        <v>1242</v>
       </c>
       <c r="E295" t="n">
         <v>1</v>
       </c>
       <c r="F295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G295" t="n">
         <v>5</v>
@@ -7232,19 +7232,19 @@
         <v>295</v>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C296" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>1058</v>
+        <v>1248</v>
       </c>
       <c r="E296" t="n">
         <v>2</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G296" t="n">
         <v>5</v>
@@ -7255,16 +7255,16 @@
         <v>296</v>
       </c>
       <c r="B297" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C297" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D297" t="n">
-        <v>1089</v>
+        <v>1257</v>
       </c>
       <c r="E297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F297" t="n">
         <v>1</v>
@@ -7278,16 +7278,16 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C298" t="n">
         <v>1</v>
       </c>
       <c r="D298" t="n">
-        <v>1111</v>
+        <v>1293</v>
       </c>
       <c r="E298" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F298" t="n">
         <v>0</v>
@@ -7301,16 +7301,16 @@
         <v>298</v>
       </c>
       <c r="B299" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C299" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D299" t="n">
-        <v>1120</v>
+        <v>1294</v>
       </c>
       <c r="E299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F299" t="n">
         <v>0</v>
@@ -7324,19 +7324,19 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C300" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D300" t="n">
-        <v>1155</v>
+        <v>1310</v>
       </c>
       <c r="E300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G300" t="n">
         <v>5</v>
@@ -7353,7 +7353,7 @@
         <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>1179</v>
+        <v>1310</v>
       </c>
       <c r="E301" t="n">
         <v>2</v>
@@ -7362,351 +7362,6 @@
         <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>301</v>
-      </c>
-      <c r="B302" t="n">
-        <v>7</v>
-      </c>
-      <c r="C302" t="n">
-        <v>1</v>
-      </c>
-      <c r="D302" t="n">
-        <v>1181</v>
-      </c>
-      <c r="E302" t="n">
-        <v>2</v>
-      </c>
-      <c r="F302" t="n">
-        <v>1</v>
-      </c>
-      <c r="G302" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="n">
-        <v>302</v>
-      </c>
-      <c r="B303" t="n">
-        <v>1</v>
-      </c>
-      <c r="C303" t="n">
-        <v>9</v>
-      </c>
-      <c r="D303" t="n">
-        <v>1184</v>
-      </c>
-      <c r="E303" t="n">
-        <v>4</v>
-      </c>
-      <c r="F303" t="n">
-        <v>0</v>
-      </c>
-      <c r="G303" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="n">
-        <v>303</v>
-      </c>
-      <c r="B304" t="n">
-        <v>1</v>
-      </c>
-      <c r="C304" t="n">
-        <v>2</v>
-      </c>
-      <c r="D304" t="n">
-        <v>1206</v>
-      </c>
-      <c r="E304" t="n">
-        <v>1</v>
-      </c>
-      <c r="F304" t="n">
-        <v>0</v>
-      </c>
-      <c r="G304" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
-        <v>304</v>
-      </c>
-      <c r="B305" t="n">
-        <v>7</v>
-      </c>
-      <c r="C305" t="n">
-        <v>1</v>
-      </c>
-      <c r="D305" t="n">
-        <v>1213</v>
-      </c>
-      <c r="E305" t="n">
-        <v>2</v>
-      </c>
-      <c r="F305" t="n">
-        <v>0</v>
-      </c>
-      <c r="G305" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
-        <v>305</v>
-      </c>
-      <c r="B306" t="n">
-        <v>4</v>
-      </c>
-      <c r="C306" t="n">
-        <v>1</v>
-      </c>
-      <c r="D306" t="n">
-        <v>1214</v>
-      </c>
-      <c r="E306" t="n">
-        <v>1</v>
-      </c>
-      <c r="F306" t="n">
-        <v>0</v>
-      </c>
-      <c r="G306" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
-        <v>306</v>
-      </c>
-      <c r="B307" t="n">
-        <v>1</v>
-      </c>
-      <c r="C307" t="n">
-        <v>7</v>
-      </c>
-      <c r="D307" t="n">
-        <v>1223</v>
-      </c>
-      <c r="E307" t="n">
-        <v>3</v>
-      </c>
-      <c r="F307" t="n">
-        <v>0</v>
-      </c>
-      <c r="G307" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
-        <v>307</v>
-      </c>
-      <c r="B308" t="n">
-        <v>1</v>
-      </c>
-      <c r="C308" t="n">
-        <v>4</v>
-      </c>
-      <c r="D308" t="n">
-        <v>1225</v>
-      </c>
-      <c r="E308" t="n">
-        <v>1</v>
-      </c>
-      <c r="F308" t="n">
-        <v>0</v>
-      </c>
-      <c r="G308" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
-        <v>308</v>
-      </c>
-      <c r="B309" t="n">
-        <v>8</v>
-      </c>
-      <c r="C309" t="n">
-        <v>1</v>
-      </c>
-      <c r="D309" t="n">
-        <v>1241</v>
-      </c>
-      <c r="E309" t="n">
-        <v>1</v>
-      </c>
-      <c r="F309" t="n">
-        <v>1</v>
-      </c>
-      <c r="G309" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="n">
-        <v>309</v>
-      </c>
-      <c r="B310" t="n">
-        <v>1</v>
-      </c>
-      <c r="C310" t="n">
-        <v>6</v>
-      </c>
-      <c r="D310" t="n">
-        <v>1257</v>
-      </c>
-      <c r="E310" t="n">
-        <v>2</v>
-      </c>
-      <c r="F310" t="n">
-        <v>1</v>
-      </c>
-      <c r="G310" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="n">
-        <v>310</v>
-      </c>
-      <c r="B311" t="n">
-        <v>1</v>
-      </c>
-      <c r="C311" t="n">
-        <v>7</v>
-      </c>
-      <c r="D311" t="n">
-        <v>1258</v>
-      </c>
-      <c r="E311" t="n">
-        <v>1</v>
-      </c>
-      <c r="F311" t="n">
-        <v>1</v>
-      </c>
-      <c r="G311" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
-        <v>311</v>
-      </c>
-      <c r="B312" t="n">
-        <v>1</v>
-      </c>
-      <c r="C312" t="n">
-        <v>7</v>
-      </c>
-      <c r="D312" t="n">
-        <v>1293</v>
-      </c>
-      <c r="E312" t="n">
-        <v>2</v>
-      </c>
-      <c r="F312" t="n">
-        <v>0</v>
-      </c>
-      <c r="G312" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
-        <v>312</v>
-      </c>
-      <c r="B313" t="n">
-        <v>4</v>
-      </c>
-      <c r="C313" t="n">
-        <v>1</v>
-      </c>
-      <c r="D313" t="n">
-        <v>1294</v>
-      </c>
-      <c r="E313" t="n">
-        <v>3</v>
-      </c>
-      <c r="F313" t="n">
-        <v>0</v>
-      </c>
-      <c r="G313" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>313</v>
-      </c>
-      <c r="B314" t="n">
-        <v>5</v>
-      </c>
-      <c r="C314" t="n">
-        <v>3</v>
-      </c>
-      <c r="D314" t="n">
-        <v>1296</v>
-      </c>
-      <c r="E314" t="n">
-        <v>1</v>
-      </c>
-      <c r="F314" t="n">
-        <v>1</v>
-      </c>
-      <c r="G314" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
-        <v>314</v>
-      </c>
-      <c r="B315" t="n">
-        <v>8</v>
-      </c>
-      <c r="C315" t="n">
-        <v>1</v>
-      </c>
-      <c r="D315" t="n">
-        <v>1300</v>
-      </c>
-      <c r="E315" t="n">
-        <v>1</v>
-      </c>
-      <c r="F315" t="n">
-        <v>0</v>
-      </c>
-      <c r="G315" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
-        <v>315</v>
-      </c>
-      <c r="B316" t="n">
-        <v>1</v>
-      </c>
-      <c r="C316" t="n">
-        <v>7</v>
-      </c>
-      <c r="D316" t="n">
-        <v>1310</v>
-      </c>
-      <c r="E316" t="n">
-        <v>2</v>
-      </c>
-      <c r="F316" t="n">
-        <v>1</v>
-      </c>
-      <c r="G316" t="n">
         <v>5</v>
       </c>
     </row>
